--- a/MAESTRIA/TIPOLOGIA ESTRUCTURAL/TRABAJO FINAL/MEMORIA CALCULO HOSPITAL LUZ VIDA.xlsx
+++ b/MAESTRIA/TIPOLOGIA ESTRUCTURAL/TRABAJO FINAL/MEMORIA CALCULO HOSPITAL LUZ VIDA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ubicacion C a D\Documentos\gitdocs-2026\MAESTRIA\TIPOLOGIA ESTRUCTURAL\TRABAJO FINAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D68F81-E333-45E3-9652-0C9AA4AC571B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D467D076-86BD-4122-9F05-08BF99896753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{A6F4C03D-0FB8-4EB4-81C4-6D3248E700FE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{A6F4C03D-0FB8-4EB4-81C4-6D3248E700FE}"/>
   </bookViews>
   <sheets>
     <sheet name="PREDIMENCIONAMIENTO" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="350">
   <si>
     <t xml:space="preserve">Uso: </t>
   </si>
@@ -1071,6 +1071,12 @@
   </si>
   <si>
     <t>Nivel5</t>
+  </si>
+  <si>
+    <t>Story4</t>
+  </si>
+  <si>
+    <t>Story5</t>
   </si>
 </sst>
 </file>
@@ -1098,7 +1104,7 @@
     <numFmt numFmtId="181" formatCode="0\ &quot;superior&quot;"/>
     <numFmt numFmtId="182" formatCode="0\ &quot;inferior&quot;"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1128,6 +1134,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="20"/>
+      <color theme="1"/>
       <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
@@ -1224,7 +1238,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1300,11 +1314,140 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1516,10 +1659,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="169" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1529,15 +1682,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1546,16 +1711,16 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1565,10 +1730,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1576,63 +1747,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1666,7 +1826,17 @@
   <c:chart>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.12165382797866102"/>
+          <c:y val="2.8265697557036139E-2"/>
+          <c:w val="0.83426326047638844"/>
+          <c:h val="0.77660687629067571"/>
+        </c:manualLayout>
+      </c:layout>
       <c:scatterChart>
         <c:scatterStyle val="smoothMarker"/>
         <c:varyColors val="0"/>
@@ -2769,7 +2939,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>ESPECTRO!$K$322</c:f>
+              <c:f>ESPECTRO!$K$330</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2804,7 +2974,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>ESPECTRO!$K$323:$K$326</c:f>
+              <c:f>ESPECTRO!$K$333:$K$336</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -2825,18 +2995,18 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>ESPECTRO!$D$323:$D$326</c:f>
+              <c:f>ESPECTRO!$D$333:$D$336</c:f>
               <c:numCache>
                 <c:formatCode>0.00"m"</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>9</c:v>
+                  <c:v>9.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6</c:v>
+                  <c:v>6.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -2856,7 +3026,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>ESPECTRO!$L$322</c:f>
+              <c:f>ESPECTRO!$L$330</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2891,7 +3061,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>ESPECTRO!$L$323:$L$326</c:f>
+              <c:f>ESPECTRO!$L$333:$L$336</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -2912,18 +3082,18 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>ESPECTRO!$D$323:$D$326</c:f>
+              <c:f>ESPECTRO!$D$333:$D$336</c:f>
               <c:numCache>
                 <c:formatCode>0.00"m"</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>9</c:v>
+                  <c:v>9.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6</c:v>
+                  <c:v>6.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -2943,7 +3113,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>ESPECTRO!$M$322</c:f>
+              <c:f>ESPECTRO!$M$330</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2978,7 +3148,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>ESPECTRO!$M$323:$M$326</c:f>
+              <c:f>ESPECTRO!$M$333:$M$336</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -2999,18 +3169,18 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>ESPECTRO!$D$323:$D$326</c:f>
+              <c:f>ESPECTRO!$D$333:$D$336</c:f>
               <c:numCache>
                 <c:formatCode>0.00"m"</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>9</c:v>
+                  <c:v>9.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6</c:v>
+                  <c:v>6.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -3323,7 +3493,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>ESPECTRO!$I$322</c:f>
+              <c:f>ESPECTRO!$I$330</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3358,7 +3528,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>ESPECTRO!$I$323:$I$326</c:f>
+              <c:f>ESPECTRO!$I$333:$I$336</c:f>
               <c:numCache>
                 <c:formatCode>0.000"cm"</c:formatCode>
                 <c:ptCount val="4"/>
@@ -3379,18 +3549,18 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>ESPECTRO!$D$323:$D$326</c:f>
+              <c:f>ESPECTRO!$D$333:$D$336</c:f>
               <c:numCache>
                 <c:formatCode>0.00"m"</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>9</c:v>
+                  <c:v>9.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6</c:v>
+                  <c:v>6.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -3410,7 +3580,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>ESPECTRO!$J$322</c:f>
+              <c:f>ESPECTRO!$J$330</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3445,7 +3615,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>ESPECTRO!$J$323:$J$326</c:f>
+              <c:f>ESPECTRO!$J$333:$J$336</c:f>
               <c:numCache>
                 <c:formatCode>0.000"cm"</c:formatCode>
                 <c:ptCount val="4"/>
@@ -3466,18 +3636,18 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>ESPECTRO!$D$323:$D$326</c:f>
+              <c:f>ESPECTRO!$D$333:$D$336</c:f>
               <c:numCache>
                 <c:formatCode>0.00"m"</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>9</c:v>
+                  <c:v>9.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6</c:v>
+                  <c:v>6.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -3497,7 +3667,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>ESPECTRO!$N$322</c:f>
+              <c:f>ESPECTRO!$N$330</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3532,7 +3702,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>ESPECTRO!$N$323:$N$326</c:f>
+              <c:f>ESPECTRO!$N$333:$N$336</c:f>
               <c:numCache>
                 <c:formatCode>0.000"cm"</c:formatCode>
                 <c:ptCount val="4"/>
@@ -3553,18 +3723,18 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>ESPECTRO!$D$323:$D$326</c:f>
+              <c:f>ESPECTRO!$D$333:$D$336</c:f>
               <c:numCache>
                 <c:formatCode>0.00"m"</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>9</c:v>
+                  <c:v>9.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6</c:v>
+                  <c:v>6.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -3877,7 +4047,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>ESPECTRO!$G$322</c:f>
+              <c:f>ESPECTRO!$G$330</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3912,7 +4082,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>ESPECTRO!$G$323:$G$326</c:f>
+              <c:f>ESPECTRO!$G$333:$G$336</c:f>
               <c:numCache>
                 <c:formatCode>0.000"cm"</c:formatCode>
                 <c:ptCount val="4"/>
@@ -3933,18 +4103,18 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>ESPECTRO!$D$323:$D$326</c:f>
+              <c:f>ESPECTRO!$D$333:$D$336</c:f>
               <c:numCache>
                 <c:formatCode>0.00"m"</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>9</c:v>
+                  <c:v>9.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6</c:v>
+                  <c:v>6.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -3964,7 +4134,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>ESPECTRO!$H$322</c:f>
+              <c:f>ESPECTRO!$H$330</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3999,7 +4169,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>ESPECTRO!$H$323:$H$326</c:f>
+              <c:f>ESPECTRO!$H$333:$H$336</c:f>
               <c:numCache>
                 <c:formatCode>0.000"cm"</c:formatCode>
                 <c:ptCount val="4"/>
@@ -4020,18 +4190,18 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>ESPECTRO!$D$323:$D$326</c:f>
+              <c:f>ESPECTRO!$D$333:$D$336</c:f>
               <c:numCache>
                 <c:formatCode>0.00"m"</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>9</c:v>
+                  <c:v>9.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6</c:v>
+                  <c:v>6.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -6989,8 +7159,8 @@
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>380958</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>173429</xdr:rowOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>1151</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7077,8 +7247,8 @@
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>668215</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>173509</xdr:rowOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>1231</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7120,7 +7290,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>371475</xdr:colOff>
+      <xdr:colOff>371476</xdr:colOff>
       <xdr:row>40</xdr:row>
       <xdr:rowOff>116967</xdr:rowOff>
     </xdr:to>
@@ -7164,7 +7334,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
+      <xdr:colOff>238126</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>156981</xdr:rowOff>
     </xdr:to>
@@ -7208,7 +7378,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>414300</xdr:colOff>
+      <xdr:colOff>49865</xdr:colOff>
       <xdr:row>52</xdr:row>
       <xdr:rowOff>9917</xdr:rowOff>
     </xdr:to>
@@ -7296,7 +7466,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
+      <xdr:colOff>238126</xdr:colOff>
       <xdr:row>58</xdr:row>
       <xdr:rowOff>165837</xdr:rowOff>
     </xdr:to>
@@ -7340,7 +7510,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
+      <xdr:colOff>333376</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>1959</xdr:rowOff>
     </xdr:to>
@@ -7384,7 +7554,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>349172</xdr:colOff>
+      <xdr:colOff>349173</xdr:colOff>
       <xdr:row>61</xdr:row>
       <xdr:rowOff>28574</xdr:rowOff>
     </xdr:to>
@@ -7465,16 +7635,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>619125</xdr:colOff>
-      <xdr:row>151</xdr:row>
-      <xdr:rowOff>152399</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>100965</xdr:colOff>
+      <xdr:row>149</xdr:row>
+      <xdr:rowOff>15239</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>523875</xdr:colOff>
-      <xdr:row>169</xdr:row>
-      <xdr:rowOff>142874</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>5715</xdr:colOff>
+      <xdr:row>167</xdr:row>
+      <xdr:rowOff>5714</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7507,8 +7677,8 @@
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>214170</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>518970</xdr:colOff>
       <xdr:row>172</xdr:row>
       <xdr:rowOff>142938</xdr:rowOff>
     </xdr:to>
@@ -7552,7 +7722,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>314510</xdr:colOff>
+      <xdr:colOff>314511</xdr:colOff>
       <xdr:row>175</xdr:row>
       <xdr:rowOff>47700</xdr:rowOff>
     </xdr:to>
@@ -7589,16 +7759,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>180</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>194310</xdr:colOff>
+      <xdr:row>178</xdr:row>
+      <xdr:rowOff>118110</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>187</xdr:row>
-      <xdr:rowOff>142626</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>186</xdr:row>
+      <xdr:rowOff>66426</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7621,8 +7791,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3829050" y="37738050"/>
-          <a:ext cx="3790950" cy="1590426"/>
+          <a:off x="6435090" y="31504890"/>
+          <a:ext cx="3333750" cy="1350396"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7772,7 +7942,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>590779</xdr:colOff>
+      <xdr:colOff>590778</xdr:colOff>
       <xdr:row>208</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
@@ -7899,7 +8069,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>551131</xdr:colOff>
+      <xdr:colOff>551132</xdr:colOff>
       <xdr:row>302</xdr:row>
       <xdr:rowOff>47924</xdr:rowOff>
     </xdr:to>
@@ -7937,15 +8107,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>329</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:colOff>29696</xdr:colOff>
+      <xdr:row>338</xdr:row>
+      <xdr:rowOff>94691</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>342</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:colOff>233082</xdr:colOff>
+      <xdr:row>353</xdr:row>
+      <xdr:rowOff>53789</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7974,13 +8144,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>329</xdr:row>
+      <xdr:row>339</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>695325</xdr:colOff>
-      <xdr:row>342</xdr:row>
+      <xdr:row>352</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -8012,13 +8182,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>345</xdr:row>
+      <xdr:row>355</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>358</xdr:row>
+      <xdr:row>368</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -8055,7 +8225,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
-      <xdr:colOff>386466</xdr:colOff>
+      <xdr:colOff>386467</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>26992</xdr:rowOff>
     </xdr:to>
@@ -8426,12 +8596,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="87" t="s">
+      <c r="A2" s="102" t="s">
         <v>324</v>
       </c>
-      <c r="B2" s="87"/>
-      <c r="C2" s="87"/>
-      <c r="D2" s="87"/>
+      <c r="B2" s="102"/>
+      <c r="C2" s="102"/>
+      <c r="D2" s="102"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="86" t="s">
@@ -8447,11 +8617,11 @@
       <c r="A4" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="96" t="s">
+      <c r="B4" s="104" t="s">
         <v>323</v>
       </c>
-      <c r="C4" s="96"/>
-      <c r="D4" s="96"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="104"/>
     </row>
     <row r="5" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A5" s="58" t="s">
@@ -8505,10 +8675,10 @@
       <c r="D9" s="1"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="95" t="s">
+      <c r="A21" s="103" t="s">
         <v>3</v>
       </c>
-      <c r="B21" s="95"/>
+      <c r="B21" s="103"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -8528,13 +8698,13 @@
         <f>15100*SQRT(C22)</f>
         <v>253254.48473140257</v>
       </c>
-      <c r="F22" s="100" t="s">
+      <c r="F22" s="95" t="s">
         <v>14</v>
       </c>
-      <c r="G22" s="100"/>
-      <c r="H22" s="100"/>
-      <c r="I22" s="100"/>
-      <c r="J22" s="100"/>
+      <c r="G22" s="95"/>
+      <c r="H22" s="95"/>
+      <c r="I22" s="95"/>
+      <c r="J22" s="95"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
@@ -8553,13 +8723,13 @@
       <c r="E23" s="8">
         <v>2039321.85</v>
       </c>
-      <c r="F23" s="100" t="s">
+      <c r="F23" s="95" t="s">
         <v>15</v>
       </c>
-      <c r="G23" s="100"/>
-      <c r="H23" s="100"/>
-      <c r="I23" s="100"/>
-      <c r="J23" s="100"/>
+      <c r="G23" s="95"/>
+      <c r="H23" s="95"/>
+      <c r="I23" s="95"/>
+      <c r="J23" s="95"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
@@ -8573,23 +8743,23 @@
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="100" t="s">
+      <c r="F24" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="G24" s="100"/>
-      <c r="H24" s="100"/>
-      <c r="I24" s="100"/>
-      <c r="J24" s="100"/>
+      <c r="G24" s="95"/>
+      <c r="H24" s="95"/>
+      <c r="I24" s="95"/>
+      <c r="J24" s="95"/>
     </row>
     <row r="26" spans="1:10" ht="30" x14ac:dyDescent="0.5">
-      <c r="A26" s="93" t="s">
+      <c r="A26" s="97" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="93"/>
-      <c r="C26" s="93"/>
-      <c r="D26" s="93"/>
-      <c r="E26" s="93"/>
-      <c r="F26" s="93"/>
+      <c r="B26" s="97"/>
+      <c r="C26" s="97"/>
+      <c r="D26" s="97"/>
+      <c r="E26" s="97"/>
+      <c r="F26" s="97"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
@@ -8601,10 +8771,10 @@
       <c r="E27" s="10"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="98" t="s">
+      <c r="A28" s="105" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="98"/>
+      <c r="B28" s="105"/>
       <c r="C28" s="10"/>
       <c r="D28" s="10"/>
       <c r="E28" s="10"/>
@@ -8703,12 +8873,12 @@
       <c r="E36" s="10"/>
     </row>
     <row r="37" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A37" s="97" t="str">
+      <c r="A37" s="99" t="str">
         <f>CONCATENATE("VX ",B32*100,"cmX",B35*100,"cm")</f>
         <v>VX 50cmX30cm</v>
       </c>
-      <c r="B37" s="97"/>
-      <c r="C37" s="97"/>
+      <c r="B37" s="99"/>
+      <c r="C37" s="99"/>
       <c r="D37" s="10"/>
       <c r="E37" s="30"/>
     </row>
@@ -8749,10 +8919,10 @@
       <c r="E40" s="10"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="98" t="s">
+      <c r="A43" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="B43" s="98"/>
+      <c r="B43" s="105"/>
       <c r="C43" s="10"/>
       <c r="D43" s="10"/>
       <c r="E43" s="10"/>
@@ -8851,12 +9021,12 @@
       <c r="E51" s="10"/>
     </row>
     <row r="52" spans="1:6" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A52" s="97" t="str">
+      <c r="A52" s="99" t="str">
         <f>CONCATENATE("VY ",B47*100,"cmX",B50*100,"cm")</f>
         <v>VY 45cmX25cm</v>
       </c>
-      <c r="B52" s="97"/>
-      <c r="C52" s="97"/>
+      <c r="B52" s="99"/>
+      <c r="C52" s="99"/>
       <c r="D52" s="10"/>
       <c r="E52" s="31"/>
     </row>
@@ -8897,10 +9067,10 @@
       <c r="E55" s="10"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="99" t="s">
+      <c r="A58" s="98" t="s">
         <v>32</v>
       </c>
-      <c r="B58" s="99"/>
+      <c r="B58" s="98"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
@@ -9125,12 +9295,12 @@
       </c>
     </row>
     <row r="78" spans="1:6" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A78" s="97" t="str">
+      <c r="A78" s="99" t="str">
         <f>CONCATENATE("C ",A76,"cmX",B76,"cm")</f>
         <v>C 45cmX55cm</v>
       </c>
-      <c r="B78" s="97"/>
-      <c r="C78" s="97"/>
+      <c r="B78" s="99"/>
+      <c r="C78" s="99"/>
       <c r="E78" s="32"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -9172,10 +9342,10 @@
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="99" t="s">
+      <c r="A87" s="98" t="s">
         <v>46</v>
       </c>
-      <c r="B87" s="99"/>
+      <c r="B87" s="98"/>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="11" t="s">
@@ -9259,42 +9429,42 @@
       </c>
     </row>
     <row r="99" spans="1:6" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A99" s="97" t="str">
+      <c r="A99" s="99" t="str">
         <f>CONCATENATE("Losa ",B96," cm")</f>
         <v>Losa 14 cm</v>
       </c>
-      <c r="B99" s="97"/>
-      <c r="C99" s="97"/>
+      <c r="B99" s="99"/>
+      <c r="C99" s="99"/>
       <c r="E99" s="16"/>
     </row>
     <row r="102" spans="1:6" ht="30" x14ac:dyDescent="0.5">
-      <c r="A102" s="93" t="s">
+      <c r="A102" s="97" t="s">
         <v>55</v>
       </c>
-      <c r="B102" s="93"/>
-      <c r="C102" s="93"/>
-      <c r="D102" s="93"/>
-      <c r="E102" s="93"/>
-      <c r="F102" s="93"/>
+      <c r="B102" s="97"/>
+      <c r="C102" s="97"/>
+      <c r="D102" s="97"/>
+      <c r="E102" s="97"/>
+      <c r="F102" s="97"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C104" s="92" t="s">
+      <c r="C104" s="100" t="s">
         <v>66</v>
       </c>
-      <c r="D104" s="92"/>
-      <c r="E104" s="92"/>
+      <c r="D104" s="100"/>
+      <c r="E104" s="100"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C105" s="94"/>
-      <c r="D105" s="94"/>
-      <c r="E105" s="94"/>
+      <c r="C105" s="96"/>
+      <c r="D105" s="96"/>
+      <c r="E105" s="96"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="88" t="s">
+      <c r="A106" s="101" t="s">
         <v>56</v>
       </c>
-      <c r="B106" s="88"/>
-      <c r="C106" s="88"/>
+      <c r="B106" s="101"/>
+      <c r="C106" s="101"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B108" s="19" t="s">
@@ -9342,11 +9512,11 @@
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A115" s="88" t="s">
+      <c r="A115" s="101" t="s">
         <v>63</v>
       </c>
-      <c r="B115" s="88"/>
-      <c r="C115" s="88"/>
+      <c r="B115" s="101"/>
+      <c r="C115" s="101"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B117" s="19" t="s">
@@ -9386,18 +9556,18 @@
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C123" s="92" t="s">
+      <c r="C123" s="100" t="s">
         <v>67</v>
       </c>
-      <c r="D123" s="92"/>
-      <c r="E123" s="92"/>
+      <c r="D123" s="100"/>
+      <c r="E123" s="100"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" s="88" t="s">
+      <c r="A125" s="101" t="s">
         <v>68</v>
       </c>
-      <c r="B125" s="88"/>
-      <c r="C125" s="88"/>
+      <c r="B125" s="101"/>
+      <c r="C125" s="101"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B127" s="11" t="s">
@@ -9406,11 +9576,11 @@
       <c r="C127" s="33">
         <v>163</v>
       </c>
-      <c r="D127" s="89" t="s">
+      <c r="D127" s="93" t="s">
         <v>72</v>
       </c>
-      <c r="E127" s="90"/>
-      <c r="F127" s="90"/>
+      <c r="E127" s="94"/>
+      <c r="F127" s="94"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B128" s="11" t="s">
@@ -9420,11 +9590,11 @@
         <f>0.01*2000</f>
         <v>20</v>
       </c>
-      <c r="D128" s="89" t="s">
+      <c r="D128" s="93" t="s">
         <v>73</v>
       </c>
-      <c r="E128" s="90"/>
-      <c r="F128" s="90"/>
+      <c r="E128" s="94"/>
+      <c r="F128" s="94"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B129" s="19"/>
@@ -9449,11 +9619,11 @@
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A134" s="88" t="s">
+      <c r="A134" s="101" t="s">
         <v>74</v>
       </c>
-      <c r="B134" s="88"/>
-      <c r="C134" s="88"/>
+      <c r="B134" s="101"/>
+      <c r="C134" s="101"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B136" s="11" t="s">
@@ -9462,11 +9632,11 @@
       <c r="C136" s="33">
         <v>163</v>
       </c>
-      <c r="D136" s="89" t="s">
+      <c r="D136" s="93" t="s">
         <v>72</v>
       </c>
-      <c r="E136" s="90"/>
-      <c r="F136" s="90"/>
+      <c r="E136" s="94"/>
+      <c r="F136" s="94"/>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B137" s="11" t="s">
@@ -9476,11 +9646,11 @@
         <f>0.01*2000</f>
         <v>20</v>
       </c>
-      <c r="D137" s="89" t="s">
+      <c r="D137" s="93" t="s">
         <v>73</v>
       </c>
-      <c r="E137" s="90"/>
-      <c r="F137" s="90"/>
+      <c r="E137" s="94"/>
+      <c r="F137" s="94"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B138" s="19"/>
@@ -9526,21 +9696,21 @@
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A146" s="91" t="s">
+      <c r="A146" s="92" t="s">
         <v>77</v>
       </c>
-      <c r="B146" s="91"/>
+      <c r="B146" s="92"/>
       <c r="C146" s="36">
         <f>C140+C144</f>
         <v>240</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A149" s="88" t="s">
+      <c r="A149" s="101" t="s">
         <v>89</v>
       </c>
-      <c r="B149" s="88"/>
-      <c r="C149" s="88"/>
+      <c r="B149" s="101"/>
+      <c r="C149" s="101"/>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B150" s="39" t="s">
@@ -9549,11 +9719,11 @@
       <c r="C150" s="40">
         <v>163</v>
       </c>
-      <c r="D150" s="89" t="s">
+      <c r="D150" s="93" t="s">
         <v>72</v>
       </c>
-      <c r="E150" s="90"/>
-      <c r="F150" s="90"/>
+      <c r="E150" s="94"/>
+      <c r="F150" s="94"/>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B151" s="11" t="s">
@@ -9563,11 +9733,11 @@
         <f>0.01*2000</f>
         <v>20</v>
       </c>
-      <c r="D151" s="89" t="s">
+      <c r="D151" s="93" t="s">
         <v>73</v>
       </c>
-      <c r="E151" s="90"/>
-      <c r="F151" s="90"/>
+      <c r="E151" s="94"/>
+      <c r="F151" s="94"/>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B152" s="19"/>
@@ -9592,255 +9762,243 @@
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="C157" s="92" t="s">
+      <c r="B157" s="118" t="s">
         <v>78</v>
       </c>
-      <c r="D157" s="92"/>
-      <c r="E157" s="92"/>
-    </row>
+      <c r="C157" s="118"/>
+      <c r="D157" s="118"/>
+      <c r="E157" s="119"/>
+      <c r="F157" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="G157" s="118"/>
+      <c r="H157" s="118"/>
+      <c r="J157" s="118" t="s">
+        <v>78</v>
+      </c>
+      <c r="K157" s="118"/>
+      <c r="L157" s="118"/>
+    </row>
+    <row r="158" spans="1:12" ht="14.4" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B159" s="123" t="s">
+      <c r="B159" s="124" t="s">
         <v>330</v>
       </c>
-      <c r="C159" s="123"/>
-      <c r="D159" s="123"/>
-      <c r="E159" s="119"/>
-      <c r="F159" s="123" t="s">
+      <c r="C159" s="125"/>
+      <c r="D159" s="126"/>
+      <c r="E159" s="84"/>
+      <c r="F159" s="124" t="s">
         <v>341</v>
       </c>
-      <c r="G159" s="123"/>
-      <c r="H159" s="123"/>
-      <c r="I159" s="119"/>
-      <c r="J159" s="123" t="s">
+      <c r="G159" s="125"/>
+      <c r="H159" s="126"/>
+      <c r="I159" s="84"/>
+      <c r="J159" s="124" t="s">
         <v>327</v>
       </c>
-      <c r="K159" s="123"/>
-      <c r="L159" s="123"/>
+      <c r="K159" s="125"/>
+      <c r="L159" s="126"/>
     </row>
     <row r="160" spans="1:12" ht="55.2" x14ac:dyDescent="0.25">
       <c r="B160" s="120" t="s">
         <v>325</v>
       </c>
-      <c r="C160" s="121">
+      <c r="C160" s="87">
         <v>250</v>
       </c>
-      <c r="D160" s="119" t="s">
+      <c r="D160" s="128" t="s">
         <v>333</v>
       </c>
-      <c r="E160" s="119"/>
+      <c r="E160" s="84"/>
       <c r="F160" s="120" t="s">
         <v>325</v>
       </c>
-      <c r="G160" s="121">
+      <c r="G160" s="87">
         <v>250</v>
       </c>
-      <c r="H160" s="117" t="s">
+      <c r="H160" s="127" t="s">
         <v>334</v>
       </c>
-      <c r="I160" s="119"/>
+      <c r="I160" s="84"/>
       <c r="J160" s="120" t="s">
         <v>328</v>
       </c>
-      <c r="K160" s="121">
+      <c r="K160" s="87">
         <v>500</v>
       </c>
-      <c r="L160" s="117" t="s">
+      <c r="L160" s="127" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="161" spans="1:12" ht="55.2" x14ac:dyDescent="0.25">
       <c r="B161" s="120"/>
-      <c r="C161" s="121">
+      <c r="C161" s="87">
         <v>75</v>
       </c>
-      <c r="D161" s="119" t="s">
+      <c r="D161" s="128" t="s">
         <v>80</v>
       </c>
-      <c r="E161" s="119"/>
+      <c r="E161" s="84"/>
       <c r="F161" s="120"/>
-      <c r="G161" s="121">
+      <c r="G161" s="87">
         <v>75</v>
       </c>
-      <c r="H161" s="119" t="s">
+      <c r="H161" s="128" t="s">
         <v>80</v>
       </c>
-      <c r="I161" s="119"/>
+      <c r="I161" s="84"/>
       <c r="J161" s="120" t="s">
         <v>336</v>
       </c>
-      <c r="K161" s="121">
+      <c r="K161" s="87">
         <v>250</v>
       </c>
-      <c r="L161" s="117" t="s">
+      <c r="L161" s="127" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B162" s="120"/>
-      <c r="C162" s="124">
+      <c r="C162" s="89">
         <v>500</v>
       </c>
-      <c r="D162" s="119"/>
-      <c r="E162" s="119"/>
+      <c r="D162" s="128"/>
+      <c r="E162" s="84"/>
       <c r="F162" s="120"/>
-      <c r="G162" s="124">
+      <c r="G162" s="89">
         <v>325</v>
       </c>
-      <c r="H162" s="119"/>
-      <c r="I162" s="119"/>
+      <c r="H162" s="128"/>
+      <c r="I162" s="84"/>
       <c r="J162" s="120"/>
-      <c r="K162" s="121">
+      <c r="K162" s="87">
         <v>75</v>
       </c>
-      <c r="L162" s="119" t="s">
+      <c r="L162" s="128" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="163" spans="1:12" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="B163" s="114" t="s">
+    <row r="163" spans="1:12" ht="55.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B163" s="121" t="s">
         <v>79</v>
       </c>
-      <c r="C163" s="122">
+      <c r="C163" s="88">
         <v>500</v>
       </c>
-      <c r="D163" s="112" t="s">
+      <c r="D163" s="130" t="s">
         <v>329</v>
       </c>
-      <c r="E163" s="119"/>
-      <c r="F163" s="120" t="s">
+      <c r="E163" s="84"/>
+      <c r="F163" s="122" t="s">
         <v>79</v>
       </c>
-      <c r="G163" s="121">
+      <c r="G163" s="123">
         <v>500</v>
       </c>
-      <c r="H163" s="117" t="s">
+      <c r="H163" s="129" t="s">
         <v>335</v>
       </c>
-      <c r="I163" s="119"/>
+      <c r="I163" s="84"/>
       <c r="J163" s="120"/>
-      <c r="K163" s="124">
+      <c r="K163" s="89">
         <v>825</v>
       </c>
-      <c r="L163" s="119"/>
-    </row>
-    <row r="164" spans="1:12" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L163" s="128"/>
+    </row>
+    <row r="164" spans="1:12" ht="34.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B164" s="120" t="s">
         <v>332</v>
       </c>
-      <c r="C164" s="121">
+      <c r="C164" s="87">
         <v>500</v>
       </c>
-      <c r="D164" s="119" t="s">
+      <c r="D164" s="128" t="s">
         <v>331</v>
       </c>
-      <c r="E164" s="119"/>
-      <c r="F164" s="119"/>
-      <c r="G164" s="119"/>
-      <c r="H164" s="119"/>
-      <c r="I164" s="119"/>
-      <c r="J164" s="120" t="s">
+      <c r="E164" s="84"/>
+      <c r="F164" s="84"/>
+      <c r="G164" s="84"/>
+      <c r="H164" s="84"/>
+      <c r="I164" s="84"/>
+      <c r="J164" s="122" t="s">
         <v>79</v>
       </c>
-      <c r="K164" s="121">
+      <c r="K164" s="123">
         <v>300</v>
       </c>
-      <c r="L164" s="117" t="s">
+      <c r="L164" s="129" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B165" s="120"/>
-      <c r="C165" s="121"/>
-      <c r="D165" s="112"/>
-      <c r="E165" s="119"/>
-      <c r="F165" s="119"/>
-      <c r="G165" s="119"/>
-      <c r="H165" s="119"/>
-      <c r="I165" s="119"/>
-      <c r="J165" s="119"/>
-      <c r="K165" s="119"/>
-      <c r="L165" s="119"/>
+    <row r="165" spans="1:12" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B165" s="122"/>
+      <c r="C165" s="123"/>
+      <c r="D165" s="131"/>
+      <c r="E165" s="84"/>
+      <c r="F165" s="84"/>
+      <c r="G165" s="84"/>
+      <c r="H165" s="84"/>
+      <c r="I165" s="84"/>
+      <c r="J165" s="84"/>
+      <c r="K165" s="84"/>
+      <c r="L165" s="84"/>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B169" s="94" t="s">
+      <c r="B169" s="96" t="s">
         <v>81</v>
       </c>
-      <c r="C169" s="94"/>
-      <c r="D169" s="90" t="s">
+      <c r="C169" s="96"/>
+      <c r="D169" s="94" t="s">
         <v>88</v>
       </c>
-      <c r="E169" s="90"/>
-      <c r="F169" s="90"/>
+      <c r="E169" s="94"/>
+      <c r="F169" s="94"/>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A170" s="91" t="s">
+      <c r="A170" s="92" t="s">
         <v>82</v>
       </c>
-      <c r="B170" s="91"/>
+      <c r="B170" s="92"/>
       <c r="C170" s="33">
         <v>200</v>
       </c>
-      <c r="D170" s="89" t="s">
+      <c r="D170" s="93" t="s">
         <v>85</v>
       </c>
-      <c r="E170" s="90"/>
+      <c r="E170" s="94"/>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A171" s="91" t="s">
+      <c r="A171" s="92" t="s">
         <v>83</v>
       </c>
-      <c r="B171" s="91"/>
+      <c r="B171" s="92"/>
       <c r="C171" s="33">
         <v>85</v>
       </c>
-      <c r="D171" s="89" t="s">
+      <c r="D171" s="93" t="s">
         <v>86</v>
       </c>
-      <c r="E171" s="90"/>
+      <c r="E171" s="94"/>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A172" s="91" t="s">
+      <c r="A172" s="92" t="s">
         <v>84</v>
       </c>
-      <c r="B172" s="91"/>
+      <c r="B172" s="92"/>
       <c r="C172" s="33">
         <f>10*14</f>
         <v>140</v>
       </c>
-      <c r="D172" s="89" t="s">
+      <c r="D172" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="E172" s="90"/>
+      <c r="E172" s="94"/>
     </row>
   </sheetData>
-  <mergeCells count="43">
-    <mergeCell ref="A171:B171"/>
-    <mergeCell ref="A172:B172"/>
-    <mergeCell ref="D170:E170"/>
-    <mergeCell ref="D171:E171"/>
-    <mergeCell ref="D172:E172"/>
-    <mergeCell ref="F22:J22"/>
-    <mergeCell ref="F23:J23"/>
-    <mergeCell ref="F24:J24"/>
-    <mergeCell ref="B169:C169"/>
-    <mergeCell ref="A170:B170"/>
-    <mergeCell ref="D169:F169"/>
-    <mergeCell ref="B159:D159"/>
-    <mergeCell ref="F159:H159"/>
-    <mergeCell ref="J159:L159"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A78:C78"/>
-    <mergeCell ref="A87:B87"/>
-    <mergeCell ref="A99:C99"/>
-    <mergeCell ref="C157:E157"/>
-    <mergeCell ref="D150:F150"/>
-    <mergeCell ref="D151:F151"/>
-    <mergeCell ref="A149:C149"/>
-    <mergeCell ref="C123:E123"/>
-    <mergeCell ref="A125:C125"/>
-    <mergeCell ref="D127:F127"/>
-    <mergeCell ref="D128:F128"/>
+  <mergeCells count="45">
+    <mergeCell ref="B157:D157"/>
+    <mergeCell ref="F157:H157"/>
+    <mergeCell ref="J157:L157"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A134:C134"/>
     <mergeCell ref="D136:F136"/>
@@ -9857,6 +10015,32 @@
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A43:B43"/>
+    <mergeCell ref="D151:F151"/>
+    <mergeCell ref="A149:C149"/>
+    <mergeCell ref="C123:E123"/>
+    <mergeCell ref="A125:C125"/>
+    <mergeCell ref="D127:F127"/>
+    <mergeCell ref="D128:F128"/>
+    <mergeCell ref="F22:J22"/>
+    <mergeCell ref="F23:J23"/>
+    <mergeCell ref="F24:J24"/>
+    <mergeCell ref="B169:C169"/>
+    <mergeCell ref="A170:B170"/>
+    <mergeCell ref="D169:F169"/>
+    <mergeCell ref="B159:D159"/>
+    <mergeCell ref="F159:H159"/>
+    <mergeCell ref="J159:L159"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A78:C78"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="A99:C99"/>
+    <mergeCell ref="D150:F150"/>
+    <mergeCell ref="A171:B171"/>
+    <mergeCell ref="A172:B172"/>
+    <mergeCell ref="D170:E170"/>
+    <mergeCell ref="D171:E171"/>
+    <mergeCell ref="D172:E172"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B35 B50" xr:uid="{328BDB17-1174-4B69-8810-57AED7F9974B}">
@@ -9871,33 +10055,39 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38998E82-9B81-4431-A442-69E8B4266069}">
-  <dimension ref="A2:R326"/>
+  <dimension ref="A2:R336"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="15.375" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="14" max="14" width="12.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="98" t="s">
         <v>90</v>
       </c>
+      <c r="B2" s="98"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="91" t="s">
+      <c r="A4" s="92" t="s">
         <v>91</v>
       </c>
-      <c r="B4" s="91"/>
-      <c r="C4" s="115">
+      <c r="B4" s="92"/>
+      <c r="C4" s="5">
         <v>750</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="91" t="s">
+      <c r="A5" s="92" t="s">
         <v>92</v>
       </c>
-      <c r="B5" s="91"/>
+      <c r="B5" s="92"/>
       <c r="C5" s="18">
         <v>5</v>
       </c>
@@ -9906,66 +10096,66 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="91" t="s">
+      <c r="A6" s="92" t="s">
         <v>93</v>
       </c>
-      <c r="B6" s="91"/>
+      <c r="B6" s="92"/>
       <c r="C6" s="21">
         <f>C4*C5</f>
         <v>3750</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="91" t="s">
+      <c r="A7" s="92" t="s">
         <v>94</v>
       </c>
-      <c r="B7" s="91"/>
+      <c r="B7" s="92"/>
       <c r="C7" s="18">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="108" t="s">
+      <c r="A8" s="114" t="s">
         <v>95</v>
       </c>
-      <c r="B8" s="108"/>
+      <c r="B8" s="114"/>
       <c r="C8" s="42">
         <f>ROUNDUP(C6/C7,0)</f>
         <v>341</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="106" t="s">
+      <c r="A9" s="116" t="s">
         <v>103</v>
       </c>
-      <c r="B9" s="106"/>
-      <c r="C9" s="125" t="s">
+      <c r="B9" s="116"/>
+      <c r="C9" s="90" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="90" t="s">
+      <c r="A10" s="94" t="s">
         <v>97</v>
       </c>
-      <c r="B10" s="90"/>
+      <c r="B10" s="94"/>
       <c r="C10" s="43" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="88" t="s">
+      <c r="A12" s="101" t="s">
         <v>98</v>
       </c>
-      <c r="B12" s="88"/>
+      <c r="B12" s="101"/>
       <c r="L12" s="41" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="91" t="s">
+      <c r="A14" s="92" t="s">
         <v>99</v>
       </c>
-      <c r="B14" s="91"/>
+      <c r="B14" s="92"/>
       <c r="C14" s="45">
         <v>0.16</v>
       </c>
@@ -9975,30 +10165,30 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="107" t="s">
+      <c r="A15" s="112" t="s">
         <v>100</v>
       </c>
-      <c r="B15" s="107"/>
+      <c r="B15" s="112"/>
       <c r="C15" s="19"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="88" t="s">
+      <c r="A17" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="B17" s="88"/>
+      <c r="B17" s="101"/>
     </row>
     <row r="18" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="126" t="s">
+      <c r="A18" s="113" t="s">
         <v>339</v>
       </c>
-      <c r="B18" s="126"/>
+      <c r="B18" s="113"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="94" t="s">
+      <c r="A22" s="96" t="s">
         <v>104</v>
       </c>
-      <c r="B22" s="94"/>
-      <c r="C22" s="94"/>
+      <c r="B22" s="96"/>
+      <c r="C22" s="96"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B24" s="11" t="s">
@@ -10007,10 +10197,10 @@
       <c r="C24" s="18">
         <v>1.7</v>
       </c>
-      <c r="E24" s="90" t="s">
+      <c r="E24" s="94" t="s">
         <v>109</v>
       </c>
-      <c r="F24" s="90"/>
+      <c r="F24" s="94"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B25" s="11" t="s">
@@ -10037,10 +10227,10 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="94" t="s">
+      <c r="A29" s="96" t="s">
         <v>110</v>
       </c>
-      <c r="B29" s="94"/>
+      <c r="B29" s="96"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B30" s="11" t="s">
@@ -10059,12 +10249,12 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="94" t="s">
+      <c r="A33" s="96" t="s">
         <v>113</v>
       </c>
-      <c r="B33" s="94"/>
-      <c r="C33" s="94"/>
-      <c r="D33" s="94"/>
+      <c r="B33" s="96"/>
+      <c r="C33" s="96"/>
+      <c r="D33" s="96"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B34" s="11" t="s">
@@ -10101,11 +10291,11 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="94" t="s">
+      <c r="A40" s="96" t="s">
         <v>118</v>
       </c>
-      <c r="B40" s="94"/>
-      <c r="C40" s="94"/>
+      <c r="B40" s="96"/>
+      <c r="C40" s="96"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B41" s="19" t="s">
@@ -10126,21 +10316,21 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="94" t="s">
+      <c r="A44" s="96" t="s">
         <v>121</v>
       </c>
-      <c r="B44" s="94"/>
+      <c r="B44" s="96"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A54" s="91" t="s">
+      <c r="A54" s="92" t="s">
         <v>122</v>
       </c>
-      <c r="B54" s="91"/>
-      <c r="C54" s="107" t="s">
+      <c r="B54" s="92"/>
+      <c r="C54" s="112" t="s">
         <v>340</v>
       </c>
-      <c r="D54" s="107"/>
-      <c r="E54" s="107"/>
+      <c r="D54" s="112"/>
+      <c r="E54" s="112"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B55" s="11" t="s">
@@ -10152,24 +10342,24 @@
       <c r="K55" s="72" t="s">
         <v>269</v>
       </c>
-      <c r="L55" s="88" t="s">
+      <c r="L55" s="101" t="s">
         <v>270</v>
       </c>
-      <c r="M55" s="88"/>
+      <c r="M55" s="101"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A57" s="94" t="s">
+      <c r="A57" s="96" t="s">
         <v>124</v>
       </c>
-      <c r="B57" s="94"/>
-      <c r="C57" s="94"/>
+      <c r="B57" s="96"/>
+      <c r="C57" s="96"/>
       <c r="K57" s="72" t="s">
         <v>269</v>
       </c>
-      <c r="L57" s="91" t="s">
+      <c r="L57" s="92" t="s">
         <v>271</v>
       </c>
-      <c r="M57" s="91"/>
+      <c r="M57" s="92"/>
       <c r="N57" t="s">
         <v>268</v>
       </c>
@@ -10185,10 +10375,10 @@
       <c r="K58" s="72" t="s">
         <v>269</v>
       </c>
-      <c r="L58" s="88" t="s">
+      <c r="L58" s="101" t="s">
         <v>272</v>
       </c>
-      <c r="M58" s="88"/>
+      <c r="M58" s="101"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B59" s="48" t="s">
@@ -10224,12 +10414,12 @@
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A64" s="94" t="s">
+      <c r="A64" s="96" t="s">
         <v>171</v>
       </c>
-      <c r="B64" s="94"/>
-      <c r="C64" s="94"/>
-      <c r="D64" s="94"/>
+      <c r="B64" s="96"/>
+      <c r="C64" s="96"/>
+      <c r="D64" s="96"/>
     </row>
     <row r="66" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C66" s="46" t="s">
@@ -11249,10 +11439,10 @@
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A170" s="88" t="s">
+      <c r="A170" s="101" t="s">
         <v>133</v>
       </c>
-      <c r="B170" s="88"/>
+      <c r="B170" s="101"/>
       <c r="D170" s="41" t="s">
         <v>138</v>
       </c>
@@ -11289,10 +11479,10 @@
         <f>C174*(C176)^C175</f>
         <v>0.30423136847641769</v>
       </c>
-      <c r="D177" s="105" t="s">
+      <c r="D177" s="115" t="s">
         <v>142</v>
       </c>
-      <c r="E177" s="94"/>
+      <c r="E177" s="96"/>
       <c r="F177" s="61" t="s">
         <v>170</v>
       </c>
@@ -11302,10 +11492,10 @@
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A179" s="88" t="s">
+      <c r="A179" s="101" t="s">
         <v>139</v>
       </c>
-      <c r="B179" s="88"/>
+      <c r="B179" s="101"/>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C181" s="51">
@@ -11334,10 +11524,10 @@
         <f>D182</f>
         <v>1.36</v>
       </c>
-      <c r="C184" s="105" t="s">
+      <c r="C184" s="115" t="s">
         <v>141</v>
       </c>
-      <c r="D184" s="94"/>
+      <c r="D184" s="96"/>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="11" t="s">
@@ -11382,67 +11572,67 @@
       </c>
     </row>
     <row r="194" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A194" s="88" t="s">
+      <c r="A194" s="101" t="s">
         <v>148</v>
       </c>
-      <c r="B194" s="88"/>
+      <c r="B194" s="101"/>
     </row>
     <row r="195" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C195" s="98" t="s">
+      <c r="C195" s="105" t="s">
         <v>160</v>
       </c>
-      <c r="D195" s="98"/>
-      <c r="E195" s="98"/>
+      <c r="D195" s="105"/>
+      <c r="E195" s="105"/>
     </row>
     <row r="196" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>149</v>
       </c>
-      <c r="B196" s="104" t="s">
+      <c r="B196" s="111" t="s">
         <v>150</v>
       </c>
-      <c r="C196" s="104" t="s">
+      <c r="C196" s="111" t="s">
         <v>151</v>
       </c>
       <c r="D196" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="E196" s="101" t="s">
+      <c r="E196" s="109" t="s">
         <v>159</v>
       </c>
-      <c r="F196" s="103" t="s">
+      <c r="F196" s="108" t="s">
         <v>161</v>
       </c>
-      <c r="G196" s="103" t="s">
+      <c r="G196" s="108" t="s">
         <v>162</v>
       </c>
-      <c r="H196" s="101" t="s">
+      <c r="H196" s="109" t="s">
         <v>163</v>
       </c>
-      <c r="I196" s="103" t="s">
+      <c r="I196" s="108" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="197" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B197" s="104"/>
-      <c r="C197" s="104"/>
+      <c r="B197" s="111"/>
+      <c r="C197" s="111"/>
       <c r="D197" s="58" t="s">
         <v>153</v>
       </c>
-      <c r="E197" s="102"/>
-      <c r="F197" s="103"/>
-      <c r="G197" s="103"/>
-      <c r="H197" s="102"/>
-      <c r="I197" s="103"/>
+      <c r="E197" s="110"/>
+      <c r="F197" s="108"/>
+      <c r="G197" s="108"/>
+      <c r="H197" s="110"/>
+      <c r="I197" s="108"/>
     </row>
     <row r="198" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B198" s="127" t="s">
+      <c r="B198" s="91" t="s">
         <v>343</v>
       </c>
-      <c r="C198" s="127" t="s">
+      <c r="C198" s="91" t="s">
         <v>155</v>
       </c>
-      <c r="D198" s="113">
+      <c r="D198">
         <v>572588.47</v>
       </c>
       <c r="E198" s="19">
@@ -11469,13 +11659,13 @@
       </c>
     </row>
     <row r="199" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B199" s="127" t="s">
+      <c r="B199" s="91" t="s">
         <v>344</v>
       </c>
-      <c r="C199" s="127" t="s">
+      <c r="C199" s="91" t="s">
         <v>158</v>
       </c>
-      <c r="D199" s="113">
+      <c r="D199">
         <v>545649.48</v>
       </c>
       <c r="E199" s="19">
@@ -11501,13 +11691,13 @@
       </c>
     </row>
     <row r="200" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B200" s="127" t="s">
+      <c r="B200" s="91" t="s">
         <v>345</v>
       </c>
-      <c r="C200" s="127" t="s">
+      <c r="C200" s="91" t="s">
         <v>158</v>
       </c>
-      <c r="D200" s="113">
+      <c r="D200">
         <v>545649.48</v>
       </c>
       <c r="E200" s="19">
@@ -11533,67 +11723,67 @@
         <v>2.4229999999999998E-3</v>
       </c>
     </row>
-    <row r="201" spans="1:13" s="113" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B201" s="127" t="s">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B201" s="91" t="s">
         <v>346</v>
       </c>
-      <c r="C201" s="127" t="s">
+      <c r="C201" s="91" t="s">
         <v>158</v>
       </c>
-      <c r="D201" s="113">
+      <c r="D201">
         <v>545649.48</v>
       </c>
-      <c r="E201" s="116">
+      <c r="E201" s="19">
         <f t="shared" ref="E201:E202" si="11">D201</f>
         <v>545649.48</v>
       </c>
-      <c r="F201" s="118">
+      <c r="F201" s="59">
         <f t="shared" ref="F201:F202" si="12">M199</f>
         <v>5.496E-3</v>
       </c>
-      <c r="G201" s="116">
+      <c r="G201" s="19">
         <v>28.4</v>
       </c>
-      <c r="H201" s="118">
+      <c r="H201" s="59">
         <f t="shared" ref="H201:H202" si="13">E201*F201^2</f>
         <v>16.48189692327168</v>
       </c>
-      <c r="I201" s="116">
+      <c r="I201" s="19">
         <f t="shared" ref="I201:I202" si="14">G201*F201</f>
         <v>0.15608639999999999</v>
       </c>
-      <c r="M201" s="117"/>
-    </row>
-    <row r="202" spans="1:13" s="113" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B202" s="127" t="s">
+      <c r="M201" s="57"/>
+    </row>
+    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B202" s="91" t="s">
         <v>347</v>
       </c>
-      <c r="C202" s="127" t="s">
+      <c r="C202" s="91" t="s">
         <v>342</v>
       </c>
-      <c r="D202" s="113">
+      <c r="D202">
         <v>411519.3</v>
       </c>
-      <c r="E202" s="116">
+      <c r="E202" s="19">
         <f t="shared" si="11"/>
         <v>411519.3</v>
       </c>
-      <c r="F202" s="118">
+      <c r="F202" s="59">
         <f t="shared" si="12"/>
         <v>2.4229999999999998E-3</v>
       </c>
-      <c r="G202" s="116">
+      <c r="G202" s="19">
         <v>29.4</v>
       </c>
-      <c r="H202" s="118">
+      <c r="H202" s="59">
         <f t="shared" si="13"/>
         <v>2.4160005924296994</v>
       </c>
-      <c r="I202" s="116">
+      <c r="I202" s="19">
         <f t="shared" si="14"/>
         <v>7.1236199999999986E-2</v>
       </c>
-      <c r="M202" s="117"/>
+      <c r="M202" s="57"/>
     </row>
     <row r="203" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G203" t="s">
@@ -11639,51 +11829,51 @@
       <c r="A212" t="s">
         <v>149</v>
       </c>
-      <c r="B212" s="104" t="s">
+      <c r="B212" s="111" t="s">
         <v>150</v>
       </c>
-      <c r="C212" s="104" t="s">
+      <c r="C212" s="111" t="s">
         <v>151</v>
       </c>
       <c r="D212" s="58" t="s">
         <v>192</v>
       </c>
-      <c r="E212" s="101" t="s">
+      <c r="E212" s="109" t="s">
         <v>159</v>
       </c>
-      <c r="F212" s="103" t="s">
+      <c r="F212" s="108" t="s">
         <v>169</v>
       </c>
-      <c r="G212" s="103" t="s">
+      <c r="G212" s="108" t="s">
         <v>162</v>
       </c>
-      <c r="H212" s="101" t="s">
+      <c r="H212" s="109" t="s">
         <v>163</v>
       </c>
-      <c r="I212" s="103" t="s">
+      <c r="I212" s="108" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B213" s="104"/>
-      <c r="C213" s="104"/>
+      <c r="B213" s="111"/>
+      <c r="C213" s="111"/>
       <c r="D213" s="58" t="s">
         <v>153</v>
       </c>
-      <c r="E213" s="102"/>
-      <c r="F213" s="103"/>
-      <c r="G213" s="103"/>
-      <c r="H213" s="102"/>
-      <c r="I213" s="103"/>
+      <c r="E213" s="110"/>
+      <c r="F213" s="108"/>
+      <c r="G213" s="108"/>
+      <c r="H213" s="110"/>
+      <c r="I213" s="108"/>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B214" s="127" t="s">
+      <c r="B214" s="91" t="s">
         <v>343</v>
       </c>
-      <c r="C214" s="127" t="s">
+      <c r="C214" s="91" t="s">
         <v>155</v>
       </c>
-      <c r="D214" s="113">
+      <c r="D214">
         <v>572588.47</v>
       </c>
       <c r="E214" s="19">
@@ -11710,13 +11900,13 @@
       </c>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B215" s="127" t="s">
+      <c r="B215" s="91" t="s">
         <v>344</v>
       </c>
-      <c r="C215" s="127" t="s">
+      <c r="C215" s="91" t="s">
         <v>158</v>
       </c>
-      <c r="D215" s="113">
+      <c r="D215">
         <v>545649.48</v>
       </c>
       <c r="E215" s="19">
@@ -11743,13 +11933,13 @@
       </c>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B216" s="127" t="s">
+      <c r="B216" s="91" t="s">
         <v>345</v>
       </c>
-      <c r="C216" s="127" t="s">
+      <c r="C216" s="91" t="s">
         <v>158</v>
       </c>
-      <c r="D216" s="113">
+      <c r="D216">
         <v>545649.48</v>
       </c>
       <c r="E216" s="19">
@@ -11775,67 +11965,67 @@
         <v>2.748E-3</v>
       </c>
     </row>
-    <row r="217" spans="1:12" s="113" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B217" s="127" t="s">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B217" s="91" t="s">
         <v>346</v>
       </c>
-      <c r="C217" s="127" t="s">
+      <c r="C217" s="91" t="s">
         <v>158</v>
       </c>
-      <c r="D217" s="113">
+      <c r="D217">
         <v>545649.48</v>
       </c>
-      <c r="E217" s="116">
+      <c r="E217" s="19">
         <f t="shared" ref="E217:E218" si="18">D217</f>
         <v>545649.48</v>
       </c>
-      <c r="F217" s="118">
+      <c r="F217" s="59">
         <f t="shared" ref="F217:F218" si="19">L215</f>
         <v>6.4140000000000004E-3</v>
       </c>
-      <c r="G217" s="116">
+      <c r="G217" s="19">
         <v>28.4</v>
       </c>
-      <c r="H217" s="118">
+      <c r="H217" s="59">
         <f t="shared" ref="H217:H218" si="20">E217*F217^2</f>
         <v>22.447690034914082</v>
       </c>
-      <c r="I217" s="116">
+      <c r="I217" s="19">
         <f t="shared" ref="I217:I218" si="21">G217*F217</f>
         <v>0.1821576</v>
       </c>
-      <c r="L217" s="117"/>
-    </row>
-    <row r="218" spans="1:12" s="113" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B218" s="127" t="s">
+      <c r="L217" s="57"/>
+    </row>
+    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B218" s="91" t="s">
         <v>347</v>
       </c>
-      <c r="C218" s="127" t="s">
+      <c r="C218" s="91" t="s">
         <v>342</v>
       </c>
-      <c r="D218" s="113">
+      <c r="D218">
         <v>411519.3</v>
       </c>
-      <c r="E218" s="116">
+      <c r="E218" s="19">
         <f t="shared" si="18"/>
         <v>411519.3</v>
       </c>
-      <c r="F218" s="118">
+      <c r="F218" s="59">
         <f t="shared" si="19"/>
         <v>2.748E-3</v>
       </c>
-      <c r="G218" s="116">
+      <c r="G218" s="19">
         <v>29.4</v>
       </c>
-      <c r="H218" s="118">
+      <c r="H218" s="59">
         <f t="shared" si="20"/>
         <v>3.1075896400271996</v>
       </c>
-      <c r="I218" s="116">
+      <c r="I218" s="19">
         <f t="shared" si="21"/>
         <v>8.0791199999999994E-2</v>
       </c>
-      <c r="L218" s="117"/>
+      <c r="L218" s="57"/>
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.25">
       <c r="G219" t="s">
@@ -11878,76 +12068,76 @@
       </c>
     </row>
     <row r="228" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A228" s="88" t="s">
+      <c r="A228" s="101" t="s">
         <v>172</v>
       </c>
-      <c r="B228" s="88"/>
+      <c r="B228" s="101"/>
     </row>
     <row r="230" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C230" s="109" t="s">
+      <c r="C230" s="107" t="s">
         <v>173</v>
       </c>
-      <c r="D230" s="109" t="s">
+      <c r="D230" s="107" t="s">
         <v>174</v>
       </c>
       <c r="E230" s="63" t="s">
         <v>175</v>
       </c>
-      <c r="F230" s="109" t="s">
+      <c r="F230" s="107" t="s">
         <v>177</v>
       </c>
-      <c r="G230" s="109" t="s">
+      <c r="G230" s="107" t="s">
         <v>178</v>
       </c>
-      <c r="H230" s="109" t="s">
+      <c r="H230" s="107" t="s">
         <v>179</v>
       </c>
-      <c r="I230" s="109" t="s">
+      <c r="I230" s="107" t="s">
         <v>180</v>
       </c>
-      <c r="J230" s="109" t="s">
+      <c r="J230" s="107" t="s">
         <v>181</v>
       </c>
-      <c r="K230" s="109" t="s">
+      <c r="K230" s="107" t="s">
         <v>182</v>
       </c>
-      <c r="L230" s="109" t="s">
+      <c r="L230" s="107" t="s">
         <v>183</v>
       </c>
-      <c r="M230" s="109" t="s">
+      <c r="M230" s="107" t="s">
         <v>184</v>
       </c>
-      <c r="N230" s="109" t="s">
+      <c r="N230" s="107" t="s">
         <v>185</v>
       </c>
-      <c r="O230" s="109" t="s">
+      <c r="O230" s="107" t="s">
         <v>186</v>
       </c>
-      <c r="P230" s="109" t="s">
+      <c r="P230" s="107" t="s">
         <v>187</v>
       </c>
-      <c r="Q230" s="109" t="s">
+      <c r="Q230" s="107" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="231" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C231" s="109"/>
-      <c r="D231" s="109"/>
+      <c r="C231" s="107"/>
+      <c r="D231" s="107"/>
       <c r="E231" s="63" t="s">
         <v>176</v>
       </c>
-      <c r="F231" s="109"/>
-      <c r="G231" s="109"/>
-      <c r="H231" s="109"/>
-      <c r="I231" s="109"/>
-      <c r="J231" s="109"/>
-      <c r="K231" s="109"/>
-      <c r="L231" s="109"/>
-      <c r="M231" s="109"/>
-      <c r="N231" s="109"/>
-      <c r="O231" s="109"/>
-      <c r="P231" s="109"/>
-      <c r="Q231" s="109"/>
+      <c r="F231" s="107"/>
+      <c r="G231" s="107"/>
+      <c r="H231" s="107"/>
+      <c r="I231" s="107"/>
+      <c r="J231" s="107"/>
+      <c r="K231" s="107"/>
+      <c r="L231" s="107"/>
+      <c r="M231" s="107"/>
+      <c r="N231" s="107"/>
+      <c r="O231" s="107"/>
+      <c r="P231" s="107"/>
+      <c r="Q231" s="107"/>
     </row>
     <row r="232" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C232" s="57" t="s">
@@ -12373,18 +12563,18 @@
       </c>
     </row>
     <row r="244" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A244" s="88" t="s">
+      <c r="A244" s="101" t="s">
         <v>190</v>
       </c>
-      <c r="B244" s="88"/>
-      <c r="C244" s="88"/>
-      <c r="D244" s="88"/>
+      <c r="B244" s="101"/>
+      <c r="C244" s="101"/>
+      <c r="D244" s="101"/>
     </row>
     <row r="246" spans="1:16" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="C246" s="109" t="s">
+      <c r="C246" s="107" t="s">
         <v>150</v>
       </c>
-      <c r="D246" s="109" t="s">
+      <c r="D246" s="107" t="s">
         <v>151</v>
       </c>
       <c r="E246" s="63" t="s">
@@ -12425,8 +12615,8 @@
       </c>
     </row>
     <row r="247" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C247" s="109"/>
-      <c r="D247" s="109"/>
+      <c r="C247" s="107"/>
+      <c r="D247" s="107"/>
       <c r="E247" s="63" t="s">
         <v>191</v>
       </c>
@@ -12459,40 +12649,40 @@
       </c>
     </row>
     <row r="248" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C248" s="127" t="s">
+      <c r="C248" s="91" t="s">
         <v>343</v>
       </c>
-      <c r="D248" s="127" t="s">
+      <c r="D248" s="91" t="s">
         <v>155</v>
       </c>
-      <c r="E248" s="113">
+      <c r="E248">
         <v>572588.47</v>
       </c>
-      <c r="F248" s="113">
+      <c r="F248">
         <v>572588.47</v>
       </c>
-      <c r="G248" s="113">
+      <c r="G248">
         <v>12.2493</v>
       </c>
-      <c r="H248" s="113">
+      <c r="H248">
         <v>16.093</v>
       </c>
-      <c r="I248" s="113">
+      <c r="I248">
         <v>572588.47</v>
       </c>
-      <c r="J248" s="113">
+      <c r="J248">
         <v>572588.47</v>
       </c>
-      <c r="K248" s="113">
+      <c r="K248">
         <v>12.2493</v>
       </c>
-      <c r="L248" s="113">
+      <c r="L248">
         <v>16.093</v>
       </c>
-      <c r="M248" s="113">
+      <c r="M248">
         <v>11.520099999999999</v>
       </c>
-      <c r="N248" s="113">
+      <c r="N248">
         <v>14.9198</v>
       </c>
       <c r="O248">
@@ -12505,40 +12695,40 @@
       </c>
     </row>
     <row r="249" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C249" s="127" t="s">
+      <c r="C249" s="91" t="s">
         <v>344</v>
       </c>
-      <c r="D249" s="127" t="s">
+      <c r="D249" s="91" t="s">
         <v>158</v>
       </c>
-      <c r="E249" s="113">
+      <c r="E249">
         <v>545649.48</v>
       </c>
-      <c r="F249" s="113">
+      <c r="F249">
         <v>545649.48</v>
       </c>
-      <c r="G249" s="113">
+      <c r="G249">
         <v>12.2958</v>
       </c>
-      <c r="H249" s="113">
+      <c r="H249">
         <v>15.9674</v>
       </c>
-      <c r="I249" s="113">
+      <c r="I249">
         <v>545649.48</v>
       </c>
-      <c r="J249" s="113">
+      <c r="J249">
         <v>545649.48</v>
       </c>
-      <c r="K249" s="113">
+      <c r="K249">
         <v>12.2958</v>
       </c>
-      <c r="L249" s="113">
+      <c r="L249">
         <v>15.9674</v>
       </c>
-      <c r="M249" s="113">
+      <c r="M249">
         <v>11.5733</v>
       </c>
-      <c r="N249" s="113">
+      <c r="N249">
         <v>14.925000000000001</v>
       </c>
       <c r="O249">
@@ -12551,40 +12741,40 @@
       </c>
     </row>
     <row r="250" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C250" s="127" t="s">
+      <c r="C250" s="91" t="s">
         <v>345</v>
       </c>
-      <c r="D250" s="127" t="s">
+      <c r="D250" s="91" t="s">
         <v>158</v>
       </c>
-      <c r="E250" s="113">
+      <c r="E250">
         <v>545649.48</v>
       </c>
-      <c r="F250" s="113">
+      <c r="F250">
         <v>545649.48</v>
       </c>
-      <c r="G250" s="113">
+      <c r="G250">
         <v>12.2958</v>
       </c>
-      <c r="H250" s="113">
+      <c r="H250">
         <v>15.9674</v>
       </c>
-      <c r="I250" s="113">
+      <c r="I250">
         <v>1091298.95</v>
       </c>
-      <c r="J250" s="113">
+      <c r="J250">
         <v>1091298.95</v>
       </c>
-      <c r="K250" s="113">
+      <c r="K250">
         <v>12.2958</v>
       </c>
-      <c r="L250" s="113">
+      <c r="L250">
         <v>15.9674</v>
       </c>
-      <c r="M250" s="113">
+      <c r="M250">
         <v>11.560499999999999</v>
       </c>
-      <c r="N250" s="113">
+      <c r="N250">
         <v>14.924300000000001</v>
       </c>
       <c r="O250">
@@ -12597,120 +12787,119 @@
       </c>
     </row>
     <row r="251" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C251" s="127" t="s">
+      <c r="C251" s="91" t="s">
         <v>346</v>
       </c>
-      <c r="D251" s="127" t="s">
+      <c r="D251" s="91" t="s">
         <v>158</v>
       </c>
-      <c r="E251" s="113">
+      <c r="E251">
         <v>545649.48</v>
       </c>
-      <c r="F251" s="113">
+      <c r="F251">
         <v>545649.48</v>
       </c>
-      <c r="G251" s="113">
+      <c r="G251">
         <v>12.2958</v>
       </c>
-      <c r="H251" s="113">
+      <c r="H251">
         <v>15.9674</v>
       </c>
-      <c r="I251" s="113">
+      <c r="I251">
         <v>1636948.43</v>
       </c>
-      <c r="J251" s="113">
+      <c r="J251">
         <v>1636948.43</v>
       </c>
-      <c r="K251" s="113">
+      <c r="K251">
         <v>12.2958</v>
       </c>
-      <c r="L251" s="113">
+      <c r="L251">
         <v>15.9674</v>
       </c>
-      <c r="M251" s="113">
+      <c r="M251">
         <v>11.543900000000001</v>
       </c>
-      <c r="N251" s="113">
+      <c r="N251">
         <v>14.9229</v>
       </c>
-      <c r="O251" s="113">
+      <c r="O251">
         <f t="shared" ref="O251:O252" si="24">K251-M251</f>
         <v>0.75189999999999912</v>
       </c>
-      <c r="P251" s="113">
+      <c r="P251">
         <f t="shared" ref="P251:P252" si="25">L251-N251</f>
         <v>1.0444999999999993</v>
       </c>
     </row>
-    <row r="252" spans="1:16" s="113" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C252" s="127" t="s">
+    <row r="252" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C252" s="91" t="s">
         <v>347</v>
       </c>
-      <c r="D252" s="127" t="s">
+      <c r="D252" s="91" t="s">
         <v>342</v>
       </c>
-      <c r="E252" s="113">
+      <c r="E252">
         <v>411519.3</v>
       </c>
-      <c r="F252" s="113">
+      <c r="F252">
         <v>411519.3</v>
       </c>
-      <c r="G252" s="113">
+      <c r="G252">
         <v>12.2906</v>
       </c>
-      <c r="H252" s="113">
+      <c r="H252">
         <v>16.139099999999999</v>
       </c>
-      <c r="I252" s="113">
+      <c r="I252">
         <v>411519.3</v>
       </c>
-      <c r="J252" s="113">
+      <c r="J252">
         <v>411519.3</v>
       </c>
-      <c r="K252" s="113">
+      <c r="K252">
         <v>12.2906</v>
       </c>
-      <c r="L252" s="113">
+      <c r="L252">
         <v>16.139099999999999</v>
       </c>
-      <c r="M252" s="113">
+      <c r="M252">
         <v>11.5869</v>
       </c>
-      <c r="N252" s="113">
+      <c r="N252">
         <v>14.925599999999999</v>
       </c>
-      <c r="O252" s="113">
+      <c r="O252">
         <f t="shared" si="24"/>
         <v>0.70369999999999955</v>
       </c>
-      <c r="P252" s="113">
+      <c r="P252">
         <f t="shared" si="25"/>
         <v>1.2134999999999998</v>
       </c>
     </row>
-    <row r="253" spans="1:16" s="113" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="255" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A255" s="88" t="s">
+      <c r="A255" s="101" t="s">
         <v>204</v>
       </c>
-      <c r="B255" s="88"/>
-      <c r="C255" s="88"/>
-      <c r="D255" s="88"/>
+      <c r="B255" s="101"/>
+      <c r="C255" s="101"/>
+      <c r="D255" s="101"/>
     </row>
     <row r="257" spans="3:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C257" s="109" t="s">
+      <c r="C257" s="107" t="s">
         <v>205</v>
       </c>
-      <c r="D257" s="109" t="s">
+      <c r="D257" s="107" t="s">
         <v>206</v>
       </c>
-      <c r="E257" s="109" t="s">
+      <c r="E257" s="107" t="s">
         <v>207</v>
       </c>
-      <c r="F257" s="109" t="s">
+      <c r="F257" s="107" t="s">
         <v>208</v>
       </c>
-      <c r="G257" s="109" t="s">
+      <c r="G257" s="107" t="s">
         <v>209</v>
       </c>
       <c r="H257" s="63" t="s">
@@ -12742,11 +12931,11 @@
       </c>
     </row>
     <row r="258" spans="3:18" x14ac:dyDescent="0.25">
-      <c r="C258" s="109"/>
-      <c r="D258" s="109"/>
-      <c r="E258" s="109"/>
-      <c r="F258" s="109"/>
-      <c r="G258" s="109"/>
+      <c r="C258" s="107"/>
+      <c r="D258" s="107"/>
+      <c r="E258" s="107"/>
+      <c r="F258" s="107"/>
+      <c r="G258" s="107"/>
       <c r="H258" s="63" t="s">
         <v>211</v>
       </c>
@@ -13129,10 +13318,10 @@
         <f>D269</f>
         <v>63.003500000000003</v>
       </c>
-      <c r="L269" s="110" t="s">
+      <c r="L269" s="106" t="s">
         <v>234</v>
       </c>
-      <c r="M269" s="110"/>
+      <c r="M269" s="106"/>
       <c r="N269" s="67">
         <f>J269/G269</f>
         <v>1.156889352435025</v>
@@ -13166,37 +13355,37 @@
         <f>D270</f>
         <v>63.003500000000003</v>
       </c>
-      <c r="L270" s="110" t="s">
+      <c r="L270" s="106" t="s">
         <v>235</v>
       </c>
-      <c r="M270" s="110"/>
+      <c r="M270" s="106"/>
       <c r="N270" s="67">
         <f>J270/G270</f>
         <v>1.1689373094784419</v>
       </c>
     </row>
     <row r="277" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A277" s="88" t="s">
+      <c r="A277" s="101" t="s">
         <v>238</v>
       </c>
-      <c r="B277" s="88"/>
-      <c r="C277" s="88"/>
-      <c r="D277" s="88"/>
+      <c r="B277" s="101"/>
+      <c r="C277" s="101"/>
+      <c r="D277" s="101"/>
     </row>
     <row r="278" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C278" s="109" t="s">
+      <c r="C278" s="107" t="s">
         <v>205</v>
       </c>
-      <c r="D278" s="109" t="s">
+      <c r="D278" s="107" t="s">
         <v>206</v>
       </c>
-      <c r="E278" s="109" t="s">
+      <c r="E278" s="107" t="s">
         <v>207</v>
       </c>
-      <c r="F278" s="109" t="s">
+      <c r="F278" s="107" t="s">
         <v>208</v>
       </c>
-      <c r="G278" s="109" t="s">
+      <c r="G278" s="107" t="s">
         <v>209</v>
       </c>
       <c r="H278" s="63" t="s">
@@ -13228,11 +13417,11 @@
       </c>
     </row>
     <row r="279" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C279" s="109"/>
-      <c r="D279" s="109"/>
-      <c r="E279" s="109"/>
-      <c r="F279" s="109"/>
-      <c r="G279" s="109"/>
+      <c r="C279" s="107"/>
+      <c r="D279" s="107"/>
+      <c r="E279" s="107"/>
+      <c r="F279" s="107"/>
+      <c r="G279" s="107"/>
       <c r="H279" s="63" t="s">
         <v>211</v>
       </c>
@@ -13615,10 +13804,10 @@
         <f>D290</f>
         <v>63.003500000000003</v>
       </c>
-      <c r="L290" s="110" t="s">
+      <c r="L290" s="106" t="s">
         <v>234</v>
       </c>
-      <c r="M290" s="110"/>
+      <c r="M290" s="106"/>
       <c r="N290" s="67">
         <f>J290/G290</f>
         <v>1.1735052143576907</v>
@@ -13652,45 +13841,53 @@
         <f>D291</f>
         <v>63.003500000000003</v>
       </c>
-      <c r="L291" s="110" t="s">
+      <c r="L291" s="106" t="s">
         <v>235</v>
       </c>
-      <c r="M291" s="110"/>
+      <c r="M291" s="106"/>
       <c r="N291" s="67">
         <f>J291/G291</f>
         <v>1.1799645655724196</v>
       </c>
     </row>
-    <row r="308" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C308" s="91" t="s">
+    <row r="308" spans="2:15" ht="25.2" x14ac:dyDescent="0.45">
+      <c r="B308" s="132" t="s">
         <v>256</v>
       </c>
-      <c r="D308" s="91"/>
-      <c r="E308" s="91"/>
+      <c r="C308" s="132"/>
+      <c r="D308" s="132"/>
+      <c r="E308" s="132"/>
+      <c r="F308" s="132"/>
+      <c r="G308" s="132"/>
+      <c r="H308" s="132"/>
+      <c r="I308" s="132"/>
+      <c r="J308" s="132"/>
+      <c r="K308" s="132"/>
+      <c r="L308" s="132"/>
     </row>
     <row r="309" spans="2:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B309" s="109" t="s">
+      <c r="B309" s="107" t="s">
         <v>150</v>
       </c>
-      <c r="C309" s="109" t="s">
+      <c r="C309" s="107" t="s">
         <v>239</v>
       </c>
-      <c r="D309" s="109" t="s">
+      <c r="D309" s="107" t="s">
         <v>240</v>
       </c>
-      <c r="E309" s="109" t="s">
+      <c r="E309" s="107" t="s">
         <v>205</v>
       </c>
-      <c r="F309" s="109" t="s">
+      <c r="F309" s="107" t="s">
         <v>206</v>
       </c>
-      <c r="G309" s="109" t="s">
+      <c r="G309" s="107" t="s">
         <v>207</v>
       </c>
-      <c r="H309" s="109" t="s">
+      <c r="H309" s="107" t="s">
         <v>208</v>
       </c>
-      <c r="I309" s="109" t="s">
+      <c r="I309" s="107" t="s">
         <v>209</v>
       </c>
       <c r="J309" s="63" t="s">
@@ -13713,14 +13910,14 @@
       </c>
     </row>
     <row r="310" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B310" s="109"/>
-      <c r="C310" s="109"/>
-      <c r="D310" s="109"/>
-      <c r="E310" s="109"/>
-      <c r="F310" s="109"/>
-      <c r="G310" s="109"/>
-      <c r="H310" s="109"/>
-      <c r="I310" s="109"/>
+      <c r="B310" s="107"/>
+      <c r="C310" s="107"/>
+      <c r="D310" s="107"/>
+      <c r="E310" s="107"/>
+      <c r="F310" s="107"/>
+      <c r="G310" s="107"/>
+      <c r="H310" s="107"/>
+      <c r="I310" s="107"/>
       <c r="J310" s="63" t="s">
         <v>242</v>
       </c>
@@ -13740,95 +13937,47 @@
         <v>246</v>
       </c>
     </row>
-    <row r="311" spans="2:15" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B311" s="57" t="s">
-        <v>157</v>
-      </c>
-      <c r="C311" s="57">
-        <v>13</v>
-      </c>
-      <c r="D311" s="57">
-        <v>49</v>
-      </c>
-      <c r="E311" s="57" t="s">
-        <v>224</v>
-      </c>
-      <c r="F311" s="57" t="s">
-        <v>225</v>
-      </c>
-      <c r="G311" s="57" t="s">
-        <v>226</v>
-      </c>
-      <c r="H311" s="57"/>
-      <c r="I311" s="57"/>
-      <c r="J311" s="59">
-        <v>1.3819999999999999</v>
-      </c>
-      <c r="K311" s="59">
-        <v>0.45429999999999998</v>
-      </c>
-      <c r="L311" s="57">
-        <v>0</v>
-      </c>
-      <c r="M311" s="57">
-        <v>0</v>
-      </c>
-      <c r="N311" s="57">
-        <v>0</v>
-      </c>
-      <c r="O311" s="57">
-        <v>1.3200000000000001E-4</v>
-      </c>
-    </row>
-    <row r="312" spans="2:15" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="B312" s="57" t="s">
-        <v>157</v>
-      </c>
-      <c r="C312" s="57">
-        <v>13</v>
-      </c>
-      <c r="D312" s="57">
-        <v>49</v>
-      </c>
-      <c r="E312" s="57" t="s">
-        <v>227</v>
-      </c>
-      <c r="F312" s="57" t="s">
-        <v>225</v>
-      </c>
-      <c r="G312" s="57" t="s">
-        <v>226</v>
-      </c>
-      <c r="H312" s="57"/>
-      <c r="I312" s="57"/>
-      <c r="J312" s="59">
-        <v>0.41670000000000001</v>
-      </c>
-      <c r="K312" s="59">
-        <v>1.522</v>
-      </c>
-      <c r="L312" s="57">
-        <v>0</v>
-      </c>
-      <c r="M312" s="57">
-        <v>0</v>
-      </c>
-      <c r="N312" s="57">
-        <v>0</v>
-      </c>
-      <c r="O312" s="57">
-        <v>2.42E-4</v>
-      </c>
+    <row r="311" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B311" s="63"/>
+      <c r="C311" s="63"/>
+      <c r="D311" s="63"/>
+      <c r="E311" s="63"/>
+      <c r="F311" s="63"/>
+      <c r="G311" s="63"/>
+      <c r="H311" s="63"/>
+      <c r="I311" s="63"/>
+      <c r="J311" s="63"/>
+      <c r="K311" s="63"/>
+      <c r="L311" s="63"/>
+      <c r="M311" s="63"/>
+      <c r="N311" s="63"/>
+      <c r="O311" s="63"/>
+    </row>
+    <row r="312" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B312" s="63"/>
+      <c r="C312" s="63"/>
+      <c r="D312" s="63"/>
+      <c r="E312" s="63"/>
+      <c r="F312" s="63"/>
+      <c r="G312" s="63"/>
+      <c r="H312" s="63"/>
+      <c r="I312" s="63"/>
+      <c r="J312" s="63"/>
+      <c r="K312" s="63"/>
+      <c r="L312" s="63"/>
+      <c r="M312" s="63"/>
+      <c r="N312" s="63"/>
+      <c r="O312" s="63"/>
     </row>
     <row r="313" spans="2:15" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B313" s="57" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C313" s="57">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D313" s="57">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E313" s="57" t="s">
         <v>224</v>
@@ -13842,10 +13991,10 @@
       <c r="H313" s="57"/>
       <c r="I313" s="57"/>
       <c r="J313" s="59">
-        <v>0.99590000000000001</v>
+        <v>1.3819999999999999</v>
       </c>
       <c r="K313" s="59">
-        <v>0.32379999999999998</v>
+        <v>0.45429999999999998</v>
       </c>
       <c r="L313" s="57">
         <v>0</v>
@@ -13856,19 +14005,19 @@
       <c r="N313" s="57">
         <v>0</v>
       </c>
-      <c r="O313" s="64">
-        <v>9.3999999999999994E-5</v>
+      <c r="O313" s="57">
+        <v>1.3200000000000001E-4</v>
       </c>
     </row>
     <row r="314" spans="2:15" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B314" s="57" t="s">
-        <v>156</v>
+        <v>349</v>
       </c>
       <c r="C314" s="57">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D314" s="57">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E314" s="57" t="s">
         <v>227</v>
@@ -13882,10 +14031,10 @@
       <c r="H314" s="57"/>
       <c r="I314" s="57"/>
       <c r="J314" s="59">
-        <v>0.30049999999999999</v>
+        <v>0.41670000000000001</v>
       </c>
       <c r="K314" s="59">
-        <v>1.0841000000000001</v>
+        <v>1.522</v>
       </c>
       <c r="L314" s="57">
         <v>0</v>
@@ -13897,21 +14046,21 @@
         <v>0</v>
       </c>
       <c r="O314" s="57">
-        <v>1.7200000000000001E-4</v>
+        <v>2.42E-4</v>
       </c>
     </row>
     <row r="315" spans="2:15" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B315" s="57" t="s">
-        <v>154</v>
+        <v>349</v>
       </c>
       <c r="C315" s="57">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D315" s="57">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E315" s="57" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F315" s="57" t="s">
         <v>225</v>
@@ -13922,10 +14071,10 @@
       <c r="H315" s="57"/>
       <c r="I315" s="57"/>
       <c r="J315" s="59">
-        <v>0.41889999999999999</v>
+        <v>0.41670000000000001</v>
       </c>
       <c r="K315" s="59">
-        <v>0.13400000000000001</v>
+        <v>1.522</v>
       </c>
       <c r="L315" s="57">
         <v>0</v>
@@ -13936,22 +14085,22 @@
       <c r="N315" s="57">
         <v>0</v>
       </c>
-      <c r="O315" s="64">
-        <v>3.8999999999999999E-5</v>
+      <c r="O315" s="57">
+        <v>2.42E-4</v>
       </c>
     </row>
     <row r="316" spans="2:15" ht="27.6" x14ac:dyDescent="0.25">
       <c r="B316" s="57" t="s">
-        <v>154</v>
+        <v>348</v>
       </c>
       <c r="C316" s="57">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D316" s="57">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E316" s="57" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F316" s="57" t="s">
         <v>225</v>
@@ -13962,349 +14111,683 @@
       <c r="H316" s="57"/>
       <c r="I316" s="57"/>
       <c r="J316" s="59">
+        <v>0.99590000000000001</v>
+      </c>
+      <c r="K316" s="59">
+        <v>0.32379999999999998</v>
+      </c>
+      <c r="L316" s="57">
+        <v>0</v>
+      </c>
+      <c r="M316" s="57">
+        <v>0</v>
+      </c>
+      <c r="N316" s="57">
+        <v>0</v>
+      </c>
+      <c r="O316" s="64">
+        <v>9.3999999999999994E-5</v>
+      </c>
+    </row>
+    <row r="317" spans="2:15" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B317" s="57" t="s">
+        <v>348</v>
+      </c>
+      <c r="C317" s="57">
+        <v>14</v>
+      </c>
+      <c r="D317" s="57">
+        <v>50</v>
+      </c>
+      <c r="E317" s="57" t="s">
+        <v>224</v>
+      </c>
+      <c r="F317" s="57" t="s">
+        <v>225</v>
+      </c>
+      <c r="G317" s="57" t="s">
+        <v>226</v>
+      </c>
+      <c r="H317" s="57"/>
+      <c r="I317" s="57"/>
+      <c r="J317" s="59">
+        <v>0.99590000000000001</v>
+      </c>
+      <c r="K317" s="59">
+        <v>0.32379999999999998</v>
+      </c>
+      <c r="L317" s="57">
+        <v>0</v>
+      </c>
+      <c r="M317" s="57">
+        <v>0</v>
+      </c>
+      <c r="N317" s="57">
+        <v>0</v>
+      </c>
+      <c r="O317" s="64">
+        <v>9.3999999999999994E-5</v>
+      </c>
+    </row>
+    <row r="318" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B318" s="57"/>
+      <c r="C318" s="57"/>
+      <c r="D318" s="57"/>
+      <c r="E318" s="57"/>
+      <c r="F318" s="57"/>
+      <c r="G318" s="57"/>
+      <c r="H318" s="57"/>
+      <c r="I318" s="57"/>
+      <c r="J318" s="59"/>
+      <c r="K318" s="59"/>
+      <c r="L318" s="57"/>
+      <c r="M318" s="57"/>
+      <c r="N318" s="57"/>
+      <c r="O318" s="64"/>
+    </row>
+    <row r="319" spans="2:15" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B319" s="57" t="s">
+        <v>157</v>
+      </c>
+      <c r="C319" s="57">
+        <v>14</v>
+      </c>
+      <c r="D319" s="57">
+        <v>50</v>
+      </c>
+      <c r="E319" s="57" t="s">
+        <v>227</v>
+      </c>
+      <c r="F319" s="57" t="s">
+        <v>225</v>
+      </c>
+      <c r="G319" s="57" t="s">
+        <v>226</v>
+      </c>
+      <c r="H319" s="57"/>
+      <c r="I319" s="57"/>
+      <c r="J319" s="59">
+        <v>0.30049999999999999</v>
+      </c>
+      <c r="K319" s="59">
+        <v>1.0841000000000001</v>
+      </c>
+      <c r="L319" s="57">
+        <v>0</v>
+      </c>
+      <c r="M319" s="57">
+        <v>0</v>
+      </c>
+      <c r="N319" s="57">
+        <v>0</v>
+      </c>
+      <c r="O319" s="57">
+        <v>1.7200000000000001E-4</v>
+      </c>
+    </row>
+    <row r="320" spans="2:15" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B320" s="57" t="s">
+        <v>157</v>
+      </c>
+      <c r="C320" s="57">
+        <v>14</v>
+      </c>
+      <c r="D320" s="57">
+        <v>50</v>
+      </c>
+      <c r="E320" s="57" t="s">
+        <v>227</v>
+      </c>
+      <c r="F320" s="57" t="s">
+        <v>225</v>
+      </c>
+      <c r="G320" s="57" t="s">
+        <v>226</v>
+      </c>
+      <c r="H320" s="57"/>
+      <c r="I320" s="57"/>
+      <c r="J320" s="59">
+        <v>0.30049999999999999</v>
+      </c>
+      <c r="K320" s="59">
+        <v>1.0841000000000001</v>
+      </c>
+      <c r="L320" s="57">
+        <v>0</v>
+      </c>
+      <c r="M320" s="57">
+        <v>0</v>
+      </c>
+      <c r="N320" s="57">
+        <v>0</v>
+      </c>
+      <c r="O320" s="57">
+        <v>1.7200000000000001E-4</v>
+      </c>
+    </row>
+    <row r="321" spans="2:15" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B321" s="57" t="s">
+        <v>156</v>
+      </c>
+      <c r="C321" s="57">
+        <v>15</v>
+      </c>
+      <c r="D321" s="57">
+        <v>51</v>
+      </c>
+      <c r="E321" s="57" t="s">
+        <v>224</v>
+      </c>
+      <c r="F321" s="57" t="s">
+        <v>225</v>
+      </c>
+      <c r="G321" s="57" t="s">
+        <v>226</v>
+      </c>
+      <c r="H321" s="57"/>
+      <c r="I321" s="57"/>
+      <c r="J321" s="59">
+        <v>0.41889999999999999</v>
+      </c>
+      <c r="K321" s="59">
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="L321" s="57">
+        <v>0</v>
+      </c>
+      <c r="M321" s="57">
+        <v>0</v>
+      </c>
+      <c r="N321" s="57">
+        <v>0</v>
+      </c>
+      <c r="O321" s="64">
+        <v>3.8999999999999999E-5</v>
+      </c>
+    </row>
+    <row r="322" spans="2:15" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B322" s="57" t="s">
+        <v>156</v>
+      </c>
+      <c r="C322" s="57">
+        <v>15</v>
+      </c>
+      <c r="D322" s="57">
+        <v>51</v>
+      </c>
+      <c r="E322" s="57" t="s">
+        <v>224</v>
+      </c>
+      <c r="F322" s="57" t="s">
+        <v>225</v>
+      </c>
+      <c r="G322" s="57" t="s">
+        <v>226</v>
+      </c>
+      <c r="H322" s="57"/>
+      <c r="I322" s="57"/>
+      <c r="J322" s="59">
+        <v>0.41889999999999999</v>
+      </c>
+      <c r="K322" s="59">
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="L322" s="57">
+        <v>0</v>
+      </c>
+      <c r="M322" s="57">
+        <v>0</v>
+      </c>
+      <c r="N322" s="57">
+        <v>0</v>
+      </c>
+      <c r="O322" s="64">
+        <v>3.8999999999999999E-5</v>
+      </c>
+    </row>
+    <row r="323" spans="2:15" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B323" s="57" t="s">
+        <v>154</v>
+      </c>
+      <c r="C323" s="57">
+        <v>15</v>
+      </c>
+      <c r="D323" s="57">
+        <v>51</v>
+      </c>
+      <c r="E323" s="57" t="s">
+        <v>224</v>
+      </c>
+      <c r="F323" s="57" t="s">
+        <v>225</v>
+      </c>
+      <c r="G323" s="57" t="s">
+        <v>226</v>
+      </c>
+      <c r="H323" s="57"/>
+      <c r="I323" s="57"/>
+      <c r="J323" s="59">
+        <v>0.41889999999999999</v>
+      </c>
+      <c r="K323" s="59">
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="L323" s="57">
+        <v>0</v>
+      </c>
+      <c r="M323" s="57">
+        <v>0</v>
+      </c>
+      <c r="N323" s="57">
+        <v>0</v>
+      </c>
+      <c r="O323" s="64">
+        <v>3.8999999999999999E-5</v>
+      </c>
+    </row>
+    <row r="324" spans="2:15" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B324" s="57" t="s">
+        <v>154</v>
+      </c>
+      <c r="C324" s="57">
+        <v>15</v>
+      </c>
+      <c r="D324" s="57">
+        <v>51</v>
+      </c>
+      <c r="E324" s="57" t="s">
+        <v>227</v>
+      </c>
+      <c r="F324" s="57" t="s">
+        <v>225</v>
+      </c>
+      <c r="G324" s="57" t="s">
+        <v>226</v>
+      </c>
+      <c r="H324" s="57"/>
+      <c r="I324" s="57"/>
+      <c r="J324" s="59">
         <v>0.12640000000000001</v>
       </c>
-      <c r="K316" s="59">
+      <c r="K324" s="59">
         <v>0.44879999999999998</v>
       </c>
-      <c r="L316" s="57">
-        <v>0</v>
-      </c>
-      <c r="M316" s="57">
-        <v>0</v>
-      </c>
-      <c r="N316" s="57">
-        <v>0</v>
-      </c>
-      <c r="O316" s="64">
+      <c r="L324" s="57">
+        <v>0</v>
+      </c>
+      <c r="M324" s="57">
+        <v>0</v>
+      </c>
+      <c r="N324" s="57">
+        <v>0</v>
+      </c>
+      <c r="O324" s="64">
         <v>7.1000000000000005E-5</v>
       </c>
     </row>
-    <row r="319" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="F319" s="62" t="s">
+    <row r="327" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="F327" s="62" t="s">
         <v>249</v>
       </c>
-      <c r="G319" s="68">
+      <c r="G327" s="68">
         <v>5.5</v>
       </c>
     </row>
-    <row r="320" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="F320" s="62"/>
-      <c r="G320" s="69"/>
-    </row>
-    <row r="321" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="E321" s="88" t="s">
+    <row r="328" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="F328" s="62"/>
+      <c r="G328" s="69"/>
+    </row>
+    <row r="329" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="E329" s="101" t="s">
         <v>253</v>
       </c>
-      <c r="F321" s="88"/>
-      <c r="G321" s="88" t="s">
+      <c r="F329" s="101"/>
+      <c r="G329" s="101" t="s">
         <v>259</v>
       </c>
-      <c r="H321" s="88"/>
-      <c r="I321" s="88" t="s">
+      <c r="H329" s="101"/>
+      <c r="I329" s="101" t="s">
         <v>260</v>
       </c>
-      <c r="J321" s="88"/>
-      <c r="K321" s="88" t="s">
+      <c r="J329" s="101"/>
+      <c r="K329" s="101" t="s">
         <v>265</v>
       </c>
-      <c r="L321" s="88"/>
-    </row>
-    <row r="322" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C322" s="46" t="s">
+      <c r="L329" s="101"/>
+    </row>
+    <row r="330" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C330" s="46" t="s">
         <v>250</v>
       </c>
-      <c r="D322" s="46" t="s">
+      <c r="D330" s="46" t="s">
         <v>252</v>
       </c>
-      <c r="E322" s="46" t="s">
+      <c r="E330" s="46" t="s">
         <v>254</v>
       </c>
-      <c r="F322" s="46" t="s">
+      <c r="F330" s="46" t="s">
         <v>255</v>
       </c>
-      <c r="G322" s="46" t="s">
+      <c r="G330" s="46" t="s">
         <v>257</v>
       </c>
-      <c r="H322" s="46" t="s">
+      <c r="H330" s="46" t="s">
         <v>258</v>
       </c>
-      <c r="I322" s="46" t="s">
+      <c r="I330" s="46" t="s">
         <v>261</v>
       </c>
-      <c r="J322" s="46" t="s">
+      <c r="J330" s="46" t="s">
         <v>262</v>
       </c>
-      <c r="K322" s="46" t="s">
+      <c r="K330" s="46" t="s">
         <v>263</v>
       </c>
-      <c r="L322" s="46" t="s">
+      <c r="L330" s="46" t="s">
         <v>264</v>
       </c>
-      <c r="M322" s="46" t="s">
+      <c r="M330" s="46" t="s">
         <v>266</v>
       </c>
-      <c r="N322" s="46" t="s">
+      <c r="N330" s="46" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="323" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C323" s="11">
+    <row r="331" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C331" s="46">
+        <v>5</v>
+      </c>
+      <c r="D331" s="14">
+        <f t="shared" ref="D331:D333" si="26">3+D332</f>
+        <v>15.5</v>
+      </c>
+      <c r="E331" s="70">
+        <f>J311</f>
+        <v>0</v>
+      </c>
+      <c r="F331" s="70">
+        <f>K313</f>
+        <v>0.45429999999999998</v>
+      </c>
+      <c r="G331" s="70">
+        <f>E331*$G$327</f>
+        <v>0</v>
+      </c>
+      <c r="H331" s="70">
+        <f>F331*$G$327</f>
+        <v>2.49865</v>
+      </c>
+      <c r="I331" s="70">
+        <f>G331-G332</f>
+        <v>-2.2918500000000002</v>
+      </c>
+      <c r="J331" s="70">
+        <f>H331-H332</f>
+        <v>2.49865</v>
+      </c>
+      <c r="K331" s="11">
+        <f>I331/300</f>
+        <v>-7.6395000000000005E-3</v>
+      </c>
+      <c r="L331" s="11">
+        <f>J331/300</f>
+        <v>8.3288333333333339E-3</v>
+      </c>
+      <c r="M331" s="11">
+        <v>0.02</v>
+      </c>
+      <c r="N331" s="70">
+        <f>M331*300</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="332" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C332" s="46">
+        <v>4</v>
+      </c>
+      <c r="D332" s="14">
+        <f t="shared" si="26"/>
+        <v>12.5</v>
+      </c>
+      <c r="E332" s="70">
+        <f>J315</f>
+        <v>0.41670000000000001</v>
+      </c>
+      <c r="F332" s="70">
+        <f>K318</f>
+        <v>0</v>
+      </c>
+      <c r="G332" s="70">
+        <f t="shared" ref="G332" si="27">E332*$G$327</f>
+        <v>2.2918500000000002</v>
+      </c>
+      <c r="H332" s="70">
+        <f t="shared" ref="H332" si="28">F332*$G$327</f>
+        <v>0</v>
+      </c>
+      <c r="I332" s="70">
+        <f>G332-G333</f>
+        <v>-5.3091499999999989</v>
+      </c>
+      <c r="J332" s="70">
+        <f t="shared" ref="J332" si="29">H332-H333</f>
+        <v>-8.3710000000000004</v>
+      </c>
+      <c r="K332" s="11">
+        <f t="shared" ref="K332" si="30">I332/300</f>
+        <v>-1.7697166666666663E-2</v>
+      </c>
+      <c r="L332" s="11">
+        <f t="shared" ref="L332" si="31">J332/300</f>
+        <v>-2.7903333333333336E-2</v>
+      </c>
+      <c r="M332" s="11">
+        <v>0.02</v>
+      </c>
+      <c r="N332" s="70">
+        <f t="shared" ref="N332" si="32">M332*300</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="333" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C333" s="11">
         <v>3</v>
       </c>
-      <c r="D323" s="14">
-        <v>9</v>
-      </c>
-      <c r="E323" s="70">
-        <f>J311</f>
+      <c r="D333" s="14">
+        <f t="shared" si="26"/>
+        <v>9.5</v>
+      </c>
+      <c r="E333" s="70">
+        <f>J313</f>
         <v>1.3819999999999999</v>
       </c>
-      <c r="F323" s="70">
-        <f>K312</f>
+      <c r="F333" s="70">
+        <f>K315</f>
         <v>1.522</v>
       </c>
-      <c r="G323" s="70">
-        <f>E323*$G$319</f>
+      <c r="G333" s="70">
+        <f>E333*$G$327</f>
         <v>7.6009999999999991</v>
       </c>
-      <c r="H323" s="70">
-        <f>F323*$G$319</f>
+      <c r="H333" s="70">
+        <f>F333*$G$327</f>
         <v>8.3710000000000004</v>
       </c>
-      <c r="I323" s="70">
-        <f>G323-G324</f>
+      <c r="I333" s="70">
+        <f>G333-G334</f>
         <v>2.1235499999999989</v>
       </c>
-      <c r="J323" s="70">
-        <f>H323-H324</f>
+      <c r="J333" s="70">
+        <f>H333-H334</f>
         <v>2.4084500000000002</v>
       </c>
-      <c r="K323" s="11">
-        <f>I323/300</f>
+      <c r="K333" s="11">
+        <f>I333/300</f>
         <v>7.0784999999999963E-3</v>
       </c>
-      <c r="L323" s="11">
-        <f>J323/300</f>
+      <c r="L333" s="11">
+        <f>J333/300</f>
         <v>8.0281666666666678E-3</v>
       </c>
-      <c r="M323" s="11">
+      <c r="M333" s="11">
         <v>0.02</v>
       </c>
-      <c r="N323" s="70">
-        <f>M323*300</f>
+      <c r="N333" s="70">
+        <f>M333*300</f>
         <v>6</v>
       </c>
     </row>
-    <row r="324" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C324" s="11">
+    <row r="334" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C334" s="11">
         <v>2</v>
       </c>
-      <c r="D324" s="14">
+      <c r="D334" s="14">
+        <f>3+D335</f>
+        <v>6.5</v>
+      </c>
+      <c r="E334" s="70">
+        <f>J317</f>
+        <v>0.99590000000000001</v>
+      </c>
+      <c r="F334" s="70">
+        <f>K320</f>
+        <v>1.0841000000000001</v>
+      </c>
+      <c r="G334" s="70">
+        <f t="shared" ref="G334:G336" si="33">E334*$G$327</f>
+        <v>5.4774500000000002</v>
+      </c>
+      <c r="H334" s="70">
+        <f t="shared" ref="H334:H336" si="34">F334*$G$327</f>
+        <v>5.9625500000000002</v>
+      </c>
+      <c r="I334" s="70">
+        <f>G334-G335</f>
+        <v>3.1735000000000002</v>
+      </c>
+      <c r="J334" s="70">
+        <f t="shared" ref="J334:J336" si="35">H334-H335</f>
+        <v>3.4941500000000003</v>
+      </c>
+      <c r="K334" s="11">
+        <f t="shared" ref="K334:K336" si="36">I334/300</f>
+        <v>1.0578333333333334E-2</v>
+      </c>
+      <c r="L334" s="11">
+        <f t="shared" ref="L334:L336" si="37">J334/300</f>
+        <v>1.1647166666666669E-2</v>
+      </c>
+      <c r="M334" s="11">
+        <v>0.02</v>
+      </c>
+      <c r="N334" s="70">
+        <f t="shared" ref="N334:N336" si="38">M334*300</f>
         <v>6</v>
       </c>
-      <c r="E324" s="70">
-        <f>J313</f>
-        <v>0.99590000000000001</v>
-      </c>
-      <c r="F324" s="70">
-        <f>K314</f>
-        <v>1.0841000000000001</v>
-      </c>
-      <c r="G324" s="70">
-        <f t="shared" ref="G324:G326" si="26">E324*$G$319</f>
-        <v>5.4774500000000002</v>
-      </c>
-      <c r="H324" s="70">
-        <f t="shared" ref="H324:H326" si="27">F324*$G$319</f>
-        <v>5.9625500000000002</v>
-      </c>
-      <c r="I324" s="70">
-        <f>G324-G325</f>
-        <v>3.1735000000000002</v>
-      </c>
-      <c r="J324" s="70">
-        <f t="shared" ref="J324:J326" si="28">H324-H325</f>
-        <v>3.4941500000000003</v>
-      </c>
-      <c r="K324" s="11">
-        <f t="shared" ref="K324:K326" si="29">I324/300</f>
-        <v>1.0578333333333334E-2</v>
-      </c>
-      <c r="L324" s="11">
-        <f t="shared" ref="L324:L326" si="30">J324/300</f>
-        <v>1.1647166666666669E-2</v>
-      </c>
-      <c r="M324" s="11">
+    </row>
+    <row r="335" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C335" s="11">
+        <v>1</v>
+      </c>
+      <c r="D335" s="14">
+        <v>3.5</v>
+      </c>
+      <c r="E335" s="70">
+        <f>J323</f>
+        <v>0.41889999999999999</v>
+      </c>
+      <c r="F335" s="70">
+        <f>K324</f>
+        <v>0.44879999999999998</v>
+      </c>
+      <c r="G335" s="70">
+        <f t="shared" si="33"/>
+        <v>2.3039499999999999</v>
+      </c>
+      <c r="H335" s="70">
+        <f t="shared" si="34"/>
+        <v>2.4683999999999999</v>
+      </c>
+      <c r="I335" s="70">
+        <f t="shared" ref="I335:I336" si="39">G335-G336</f>
+        <v>2.3039499999999999</v>
+      </c>
+      <c r="J335" s="70">
+        <f t="shared" si="35"/>
+        <v>2.4683999999999999</v>
+      </c>
+      <c r="K335" s="11">
+        <f t="shared" si="36"/>
+        <v>7.6798333333333328E-3</v>
+      </c>
+      <c r="L335" s="11">
+        <f t="shared" si="37"/>
+        <v>8.2279999999999992E-3</v>
+      </c>
+      <c r="M335" s="11">
         <v>0.02</v>
       </c>
-      <c r="N324" s="70">
-        <f t="shared" ref="N324:N326" si="31">M324*300</f>
+      <c r="N335" s="70">
+        <f t="shared" si="38"/>
         <v>6</v>
       </c>
     </row>
-    <row r="325" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C325" s="11">
-        <v>1</v>
-      </c>
-      <c r="D325" s="14">
-        <v>3</v>
-      </c>
-      <c r="E325" s="70">
-        <f>J315</f>
-        <v>0.41889999999999999</v>
-      </c>
-      <c r="F325" s="70">
-        <f>K316</f>
-        <v>0.44879999999999998</v>
-      </c>
-      <c r="G325" s="70">
-        <f t="shared" si="26"/>
-        <v>2.3039499999999999</v>
-      </c>
-      <c r="H325" s="70">
-        <f t="shared" si="27"/>
-        <v>2.4683999999999999</v>
-      </c>
-      <c r="I325" s="70">
-        <f t="shared" ref="I325:I326" si="32">G325-G326</f>
-        <v>2.3039499999999999</v>
-      </c>
-      <c r="J325" s="70">
-        <f t="shared" si="28"/>
-        <v>2.4683999999999999</v>
-      </c>
-      <c r="K325" s="11">
-        <f t="shared" si="29"/>
-        <v>7.6798333333333328E-3</v>
-      </c>
-      <c r="L325" s="11">
-        <f t="shared" si="30"/>
-        <v>8.2279999999999992E-3</v>
-      </c>
-      <c r="M325" s="11">
+    <row r="336" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C336" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="D336" s="14">
+        <v>0</v>
+      </c>
+      <c r="E336" s="70">
+        <v>0</v>
+      </c>
+      <c r="F336" s="70">
+        <v>0</v>
+      </c>
+      <c r="G336" s="70">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="H336" s="70">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="I336" s="70">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="J336" s="70">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="K336" s="11">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L336" s="11">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="M336" s="11">
         <v>0.02</v>
       </c>
-      <c r="N325" s="70">
-        <f t="shared" si="31"/>
+      <c r="N336" s="70">
+        <f t="shared" si="38"/>
         <v>6</v>
       </c>
     </row>
-    <row r="326" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C326" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="D326" s="14">
-        <v>0</v>
-      </c>
-      <c r="E326" s="70">
-        <v>0</v>
-      </c>
-      <c r="F326" s="70">
-        <v>0</v>
-      </c>
-      <c r="G326" s="70">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="H326" s="70">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I326" s="70">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J326" s="70">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="K326" s="11">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="L326" s="11">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="M326" s="11">
-        <v>0.02</v>
-      </c>
-      <c r="N326" s="70">
-        <f t="shared" si="31"/>
-        <v>6</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="92">
-    <mergeCell ref="L55:M55"/>
-    <mergeCell ref="L58:M58"/>
-    <mergeCell ref="L57:M57"/>
-    <mergeCell ref="E321:F321"/>
-    <mergeCell ref="C308:E308"/>
-    <mergeCell ref="G321:H321"/>
-    <mergeCell ref="I321:J321"/>
-    <mergeCell ref="K321:L321"/>
-    <mergeCell ref="L290:M290"/>
-    <mergeCell ref="L291:M291"/>
-    <mergeCell ref="A277:D277"/>
-    <mergeCell ref="B309:B310"/>
-    <mergeCell ref="C309:C310"/>
-    <mergeCell ref="D309:D310"/>
-    <mergeCell ref="E309:E310"/>
-    <mergeCell ref="F309:F310"/>
-    <mergeCell ref="G309:G310"/>
-    <mergeCell ref="H309:H310"/>
-    <mergeCell ref="I309:I310"/>
-    <mergeCell ref="L269:M269"/>
-    <mergeCell ref="L270:M270"/>
-    <mergeCell ref="C278:C279"/>
-    <mergeCell ref="D278:D279"/>
-    <mergeCell ref="E278:E279"/>
-    <mergeCell ref="F278:F279"/>
-    <mergeCell ref="G278:G279"/>
-    <mergeCell ref="C257:C258"/>
-    <mergeCell ref="D257:D258"/>
-    <mergeCell ref="E257:E258"/>
-    <mergeCell ref="F257:F258"/>
-    <mergeCell ref="G257:G258"/>
-    <mergeCell ref="A244:D244"/>
-    <mergeCell ref="C246:C247"/>
-    <mergeCell ref="D246:D247"/>
-    <mergeCell ref="A255:D255"/>
-    <mergeCell ref="M230:M231"/>
-    <mergeCell ref="N230:N231"/>
-    <mergeCell ref="O230:O231"/>
-    <mergeCell ref="P230:P231"/>
-    <mergeCell ref="Q230:Q231"/>
-    <mergeCell ref="H230:H231"/>
-    <mergeCell ref="I230:I231"/>
-    <mergeCell ref="J230:J231"/>
-    <mergeCell ref="K230:K231"/>
-    <mergeCell ref="L230:L231"/>
-    <mergeCell ref="A228:B228"/>
-    <mergeCell ref="C230:C231"/>
-    <mergeCell ref="D230:D231"/>
-    <mergeCell ref="F230:F231"/>
-    <mergeCell ref="G230:G231"/>
-    <mergeCell ref="F196:F197"/>
-    <mergeCell ref="G196:G197"/>
-    <mergeCell ref="H196:H197"/>
-    <mergeCell ref="I196:I197"/>
-    <mergeCell ref="A194:B194"/>
-    <mergeCell ref="B196:B197"/>
-    <mergeCell ref="C196:C197"/>
-    <mergeCell ref="E196:E197"/>
-    <mergeCell ref="C195:E195"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A170:B170"/>
-    <mergeCell ref="A64:D64"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
+  <mergeCells count="93">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B308:L308"/>
+    <mergeCell ref="H212:H213"/>
+    <mergeCell ref="I212:I213"/>
+    <mergeCell ref="B212:B213"/>
+    <mergeCell ref="C212:C213"/>
+    <mergeCell ref="E212:E213"/>
+    <mergeCell ref="F212:F213"/>
+    <mergeCell ref="G212:G213"/>
     <mergeCell ref="C184:D184"/>
     <mergeCell ref="D177:E177"/>
     <mergeCell ref="A10:B10"/>
@@ -14321,13 +14804,74 @@
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="H212:H213"/>
-    <mergeCell ref="I212:I213"/>
-    <mergeCell ref="B212:B213"/>
-    <mergeCell ref="C212:C213"/>
-    <mergeCell ref="E212:E213"/>
-    <mergeCell ref="F212:F213"/>
-    <mergeCell ref="G212:G213"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A170:B170"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="F196:F197"/>
+    <mergeCell ref="G196:G197"/>
+    <mergeCell ref="H196:H197"/>
+    <mergeCell ref="I196:I197"/>
+    <mergeCell ref="A194:B194"/>
+    <mergeCell ref="B196:B197"/>
+    <mergeCell ref="C196:C197"/>
+    <mergeCell ref="E196:E197"/>
+    <mergeCell ref="C195:E195"/>
+    <mergeCell ref="A228:B228"/>
+    <mergeCell ref="C230:C231"/>
+    <mergeCell ref="D230:D231"/>
+    <mergeCell ref="F230:F231"/>
+    <mergeCell ref="G230:G231"/>
+    <mergeCell ref="N230:N231"/>
+    <mergeCell ref="O230:O231"/>
+    <mergeCell ref="P230:P231"/>
+    <mergeCell ref="Q230:Q231"/>
+    <mergeCell ref="H230:H231"/>
+    <mergeCell ref="I230:I231"/>
+    <mergeCell ref="J230:J231"/>
+    <mergeCell ref="K230:K231"/>
+    <mergeCell ref="L230:L231"/>
+    <mergeCell ref="A244:D244"/>
+    <mergeCell ref="C246:C247"/>
+    <mergeCell ref="D246:D247"/>
+    <mergeCell ref="A255:D255"/>
+    <mergeCell ref="M230:M231"/>
+    <mergeCell ref="C257:C258"/>
+    <mergeCell ref="D257:D258"/>
+    <mergeCell ref="E257:E258"/>
+    <mergeCell ref="F257:F258"/>
+    <mergeCell ref="G257:G258"/>
+    <mergeCell ref="C278:C279"/>
+    <mergeCell ref="D278:D279"/>
+    <mergeCell ref="E278:E279"/>
+    <mergeCell ref="F278:F279"/>
+    <mergeCell ref="G278:G279"/>
+    <mergeCell ref="G309:G310"/>
+    <mergeCell ref="H309:H310"/>
+    <mergeCell ref="I309:I310"/>
+    <mergeCell ref="L269:M269"/>
+    <mergeCell ref="L270:M270"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="L58:M58"/>
+    <mergeCell ref="L57:M57"/>
+    <mergeCell ref="E329:F329"/>
+    <mergeCell ref="G329:H329"/>
+    <mergeCell ref="I329:J329"/>
+    <mergeCell ref="K329:L329"/>
+    <mergeCell ref="L290:M290"/>
+    <mergeCell ref="L291:M291"/>
+    <mergeCell ref="A277:D277"/>
+    <mergeCell ref="B309:B310"/>
+    <mergeCell ref="C309:C310"/>
+    <mergeCell ref="D309:D310"/>
+    <mergeCell ref="E309:E310"/>
+    <mergeCell ref="F309:F310"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14345,10 +14889,10 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="99" t="s">
+      <c r="A4" s="98" t="s">
         <v>273</v>
       </c>
-      <c r="B4" s="99"/>
+      <c r="B4" s="98"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -14367,18 +14911,18 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="94" t="s">
+      <c r="A9" s="96" t="s">
         <v>320</v>
       </c>
-      <c r="B9" s="94"/>
-      <c r="C9" s="90" t="s">
+      <c r="B9" s="96"/>
+      <c r="C9" s="94" t="s">
         <v>282</v>
       </c>
-      <c r="D9" s="90"/>
-      <c r="E9" s="90"/>
-      <c r="F9" s="90"/>
-      <c r="G9" s="90"/>
-      <c r="H9" s="90"/>
+      <c r="D9" s="94"/>
+      <c r="E9" s="94"/>
+      <c r="F9" s="94"/>
+      <c r="G9" s="94"/>
+      <c r="H9" s="94"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
@@ -14405,10 +14949,10 @@
       <c r="F11" t="s">
         <v>277</v>
       </c>
-      <c r="G11" s="90" t="s">
+      <c r="G11" s="94" t="s">
         <v>283</v>
       </c>
-      <c r="H11" s="90"/>
+      <c r="H11" s="94"/>
       <c r="K11" s="11"/>
       <c r="L11" s="11"/>
     </row>
@@ -14491,10 +15035,10 @@
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="94" t="s">
+      <c r="A18" s="96" t="s">
         <v>321</v>
       </c>
-      <c r="B18" s="94"/>
+      <c r="B18" s="96"/>
       <c r="K18" s="11">
         <v>10</v>
       </c>
@@ -14503,12 +15047,12 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="90" t="s">
+      <c r="A19" s="94" t="s">
         <v>285</v>
       </c>
-      <c r="B19" s="90"/>
-      <c r="C19" s="90"/>
-      <c r="D19" s="90"/>
+      <c r="B19" s="94"/>
+      <c r="C19" s="94"/>
+      <c r="D19" s="94"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
@@ -14521,10 +15065,10 @@
       <c r="F21" t="s">
         <v>277</v>
       </c>
-      <c r="G21" s="90" t="s">
+      <c r="G21" s="94" t="s">
         <v>288</v>
       </c>
-      <c r="H21" s="90"/>
+      <c r="H21" s="94"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
@@ -14570,17 +15114,17 @@
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="E30" s="90" t="s">
+      <c r="E30" s="94" t="s">
         <v>301</v>
       </c>
-      <c r="F30" s="90"/>
-      <c r="G30" s="90"/>
-      <c r="H30" s="90"/>
-      <c r="I30" s="90"/>
-      <c r="J30" s="90"/>
-      <c r="K30" s="90"/>
-      <c r="L30" s="90"/>
-      <c r="M30" s="90"/>
+      <c r="F30" s="94"/>
+      <c r="G30" s="94"/>
+      <c r="H30" s="94"/>
+      <c r="I30" s="94"/>
+      <c r="J30" s="94"/>
+      <c r="K30" s="94"/>
+      <c r="L30" s="94"/>
+      <c r="M30" s="94"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
@@ -14612,29 +15156,29 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="91" t="s">
+      <c r="A34" s="92" t="s">
         <v>297</v>
       </c>
-      <c r="B34" s="91"/>
+      <c r="B34" s="92"/>
       <c r="C34" s="81">
         <f>B6*2</f>
         <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="94" t="s">
+      <c r="A37" s="96" t="s">
         <v>302</v>
       </c>
-      <c r="B37" s="94"/>
+      <c r="B37" s="96"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="90" t="s">
+      <c r="A38" s="94" t="s">
         <v>303</v>
       </c>
-      <c r="B38" s="90"/>
-      <c r="C38" s="90"/>
-      <c r="D38" s="90"/>
-      <c r="E38" s="90"/>
+      <c r="B38" s="94"/>
+      <c r="C38" s="94"/>
+      <c r="D38" s="94"/>
+      <c r="E38" s="94"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
@@ -14643,18 +15187,18 @@
       <c r="B40" s="74">
         <v>11.95</v>
       </c>
-      <c r="E40" s="90" t="s">
+      <c r="E40" s="94" t="s">
         <v>306</v>
       </c>
-      <c r="F40" s="90"/>
-      <c r="G40" s="90"/>
-      <c r="H40" s="90"/>
-      <c r="I40" s="90"/>
-      <c r="J40" s="90"/>
-      <c r="K40" s="90"/>
-      <c r="L40" s="90"/>
-      <c r="M40" s="90"/>
-      <c r="N40" s="90"/>
+      <c r="F40" s="94"/>
+      <c r="G40" s="94"/>
+      <c r="H40" s="94"/>
+      <c r="I40" s="94"/>
+      <c r="J40" s="94"/>
+      <c r="K40" s="94"/>
+      <c r="L40" s="94"/>
+      <c r="M40" s="94"/>
+      <c r="N40" s="94"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
@@ -14669,28 +15213,28 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="99" t="s">
+      <c r="A45" s="98" t="s">
         <v>307</v>
       </c>
-      <c r="B45" s="99"/>
+      <c r="B45" s="98"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="90" t="s">
+      <c r="A47" s="94" t="s">
         <v>308</v>
       </c>
-      <c r="B47" s="90"/>
-      <c r="C47" s="90"/>
-      <c r="D47" s="90"/>
-      <c r="E47" s="90"/>
-      <c r="F47" s="90"/>
-      <c r="G47" s="90"/>
-      <c r="H47" s="90"/>
+      <c r="B47" s="94"/>
+      <c r="C47" s="94"/>
+      <c r="D47" s="94"/>
+      <c r="E47" s="94"/>
+      <c r="F47" s="94"/>
+      <c r="G47" s="94"/>
+      <c r="H47" s="94"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="94" t="s">
+      <c r="A49" s="96" t="s">
         <v>309</v>
       </c>
-      <c r="B49" s="94"/>
+      <c r="B49" s="96"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
@@ -14710,33 +15254,33 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="99" t="s">
+      <c r="A54" s="98" t="s">
         <v>310</v>
       </c>
-      <c r="B54" s="99"/>
+      <c r="B54" s="98"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D55" s="90" t="s">
+      <c r="D55" s="94" t="s">
         <v>317</v>
       </c>
-      <c r="E55" s="90"/>
-      <c r="F55" s="90"/>
+      <c r="E55" s="94"/>
+      <c r="F55" s="94"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="94" t="s">
+      <c r="A56" s="96" t="s">
         <v>311</v>
       </c>
-      <c r="B56" s="94"/>
+      <c r="B56" s="96"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="111" t="s">
+      <c r="A57" s="117" t="s">
         <v>315</v>
       </c>
-      <c r="B57" s="111"/>
-      <c r="C57" s="111"/>
-      <c r="D57" s="111"/>
-      <c r="E57" s="111"/>
-      <c r="F57" s="111"/>
+      <c r="B57" s="117"/>
+      <c r="C57" s="117"/>
+      <c r="D57" s="117"/>
+      <c r="E57" s="117"/>
+      <c r="F57" s="117"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="11" t="s">
@@ -14773,20 +15317,20 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="94" t="s">
+      <c r="A64" s="96" t="s">
         <v>318</v>
       </c>
-      <c r="B64" s="94"/>
+      <c r="B64" s="96"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="111" t="s">
+      <c r="A65" s="117" t="s">
         <v>316</v>
       </c>
-      <c r="B65" s="111"/>
-      <c r="C65" s="111"/>
-      <c r="D65" s="111"/>
-      <c r="E65" s="111"/>
-      <c r="F65" s="111"/>
+      <c r="B65" s="117"/>
+      <c r="C65" s="117"/>
+      <c r="D65" s="117"/>
+      <c r="E65" s="117"/>
+      <c r="F65" s="117"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G66" s="84"/>
@@ -14830,18 +15374,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A65:F65"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="E30:M30"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:H9"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="A18:B18"/>
     <mergeCell ref="A19:D19"/>
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="A56:B56"/>
@@ -14851,6 +15383,18 @@
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A47:H47"/>
     <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A65:F65"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="E30:M30"/>
+    <mergeCell ref="A34:B34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
